--- a/400万资产配置组合2026.xlsx
+++ b/400万资产配置组合2026.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="流水" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日报" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GA优化方案" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$26</definedName>
@@ -32,7 +33,7 @@
     <numFmt numFmtId="172" formatCode="0.0000"/>
     <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="36">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -240,8 +241,43 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -452,8 +488,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -572,6 +626,40 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -724,7 +812,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -980,6 +1068,28 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1584,10 +1694,11 @@
     <row r="1" ht="20" customHeight="1" s="1">
       <c r="A1" s="46" t="inlineStr">
         <is>
-          <t>400万资产配置 -- 投资纪律速查（V3优化版 2026-06-26）</t>
-        </is>
-      </c>
-    </row>
+          <t>400万资产配置 -- 投资纪律速查（V3优化版 2026-06-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3" ht="16.5" customHeight="1" s="1">
       <c r="A3" s="47" t="inlineStr">
         <is>
@@ -1836,6 +1947,7 @@
     </row>
     <row r="21">
       <c r="A21" s="55" t="n"/>
+      <c r="B21" s="0" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1" s="1">
       <c r="A22" s="49" t="inlineStr">
@@ -2133,6 +2245,9 @@
       <c r="D37" s="53" t="n"/>
       <c r="E37" s="53" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="0" t="n"/>
+    </row>
     <row r="39">
       <c r="A39" s="57" t="inlineStr">
         <is>
@@ -2147,6 +2262,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42" ht="16.5" customHeight="1" s="1">
       <c r="A42" s="47" t="inlineStr">
         <is>
@@ -2219,12 +2335,14 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51" ht="16.5" customHeight="1" s="1">
       <c r="A51" s="58" t="n"/>
     </row>
     <row r="52" ht="14.5" customHeight="1" s="1">
       <c r="A52" s="59" t="n"/>
     </row>
+    <row r="53"/>
     <row r="54" ht="16.5" customHeight="1" s="1">
       <c r="A54" s="58" t="n"/>
     </row>
@@ -2267,7 +2385,7 @@
     <row r="1" ht="115.2" customHeight="1" s="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>更新日期: 2026-06-26 (数据日期: 2026-06-26)</t>
+          <t>更新日期: 2026-06-27 (数据日期: 2026-06-26)</t>
         </is>
       </c>
       <c r="B1" s="16" t="inlineStr">
@@ -2437,11 +2555,7 @@
       <c r="M3" s="68" t="n">
         <v>0.13</v>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>🔴止盈第三档：浮盈13.0% &gt;= 12%，清仓止盈</t>
-        </is>
-      </c>
+      <c r="N3" s="4" t="n"/>
       <c r="O3" s="78" t="inlineStr">
         <is>
           <t>42,600份(部分建仓)</t>
@@ -19337,495 +19451,495 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B296" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C296" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D296" t="n">
+      <c r="D296" s="0" t="n">
         <v>153800</v>
       </c>
-      <c r="E296" t="n">
+      <c r="E296" s="0" t="n">
         <v>4.885</v>
       </c>
-      <c r="F296" t="n">
+      <c r="F296" s="0" t="n">
         <v>751313</v>
       </c>
-      <c r="G296" t="n">
+      <c r="G296" s="0" t="n">
         <v>4.907</v>
       </c>
-      <c r="H296" t="n">
+      <c r="H296" s="0" t="n">
         <v>-0.0279</v>
       </c>
-      <c r="I296" t="n">
+      <c r="I296" s="0" t="n">
         <v>754696.6</v>
       </c>
-      <c r="J296" t="n">
+      <c r="J296" s="0" t="n">
         <v>3383.6</v>
       </c>
-      <c r="K296" t="n">
+      <c r="K296" s="0" t="n">
         <v>0.0045</v>
       </c>
-      <c r="L296" t="n">
+      <c r="L296" s="0" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M296" t="n">
+      <c r="M296" s="0" t="n">
         <v>0.2248</v>
       </c>
-      <c r="N296" t="n">
+      <c r="N296" s="0" t="n">
         <v>0.0373</v>
       </c>
-      <c r="O296" t="inlineStr">
+      <c r="O296" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B297" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
+      <c r="C297" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D297" t="n">
+      <c r="D297" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E297" s="0" t="n">
         <v>1.838</v>
       </c>
-      <c r="F297" t="n">
+      <c r="F297" s="0" t="n">
         <v>110280</v>
       </c>
-      <c r="G297" t="n">
+      <c r="G297" s="0" t="n">
         <v>2.077</v>
       </c>
-      <c r="H297" t="n">
+      <c r="H297" s="0" t="n">
         <v>-0.0194</v>
       </c>
-      <c r="I297" t="n">
+      <c r="I297" s="0" t="n">
         <v>124620</v>
       </c>
-      <c r="J297" t="n">
+      <c r="J297" s="0" t="n">
         <v>14340</v>
       </c>
-      <c r="K297" t="n">
+      <c r="K297" s="0" t="n">
         <v>0.13</v>
       </c>
-      <c r="L297" t="n">
+      <c r="L297" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M297" t="n">
+      <c r="M297" s="0" t="n">
         <v>0.0371</v>
       </c>
-      <c r="N297" t="n">
+      <c r="N297" s="0" t="n">
         <v>-0.0254</v>
       </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>🔴止盈第三档：浮盈13.0% &gt;= 12%，清仓止盈</t>
+      <c r="O297" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C298" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D298" t="n">
+      <c r="D298" s="0" t="n">
         <v>63000</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E298" s="0" t="n">
         <v>3.968</v>
       </c>
-      <c r="F298" t="n">
+      <c r="F298" s="0" t="n">
         <v>249984</v>
       </c>
-      <c r="G298" t="n">
+      <c r="G298" s="0" t="n">
         <v>4.215</v>
       </c>
-      <c r="H298" t="n">
+      <c r="H298" s="0" t="n">
         <v>-0.041</v>
       </c>
-      <c r="I298" t="n">
+      <c r="I298" s="0" t="n">
         <v>265545</v>
       </c>
-      <c r="J298" t="n">
+      <c r="J298" s="0" t="n">
         <v>15561</v>
       </c>
-      <c r="K298" t="n">
+      <c r="K298" s="0" t="n">
         <v>0.0622</v>
       </c>
-      <c r="L298" t="n">
+      <c r="L298" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M298" t="n">
+      <c r="M298" s="0" t="n">
         <v>0.0791</v>
       </c>
-      <c r="N298" t="n">
+      <c r="N298" s="0" t="n">
         <v>0.0166</v>
       </c>
-      <c r="O298" t="inlineStr">
+      <c r="O298" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B299" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
+      <c r="C299" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D299" t="n">
+      <c r="D299" s="0" t="n">
         <v>218000</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E299" s="0" t="n">
         <v>1.15</v>
       </c>
-      <c r="F299" t="n">
+      <c r="F299" s="0" t="n">
         <v>250700</v>
       </c>
-      <c r="G299" t="n">
+      <c r="G299" s="0" t="n">
         <v>1.081</v>
       </c>
-      <c r="H299" t="n">
+      <c r="H299" s="0" t="n">
         <v>-0.0046</v>
       </c>
-      <c r="I299" t="n">
+      <c r="I299" s="0" t="n">
         <v>235658</v>
       </c>
-      <c r="J299" t="n">
+      <c r="J299" s="0" t="n">
         <v>-15042</v>
       </c>
-      <c r="K299" t="n">
+      <c r="K299" s="0" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L299" t="n">
+      <c r="L299" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M299" t="n">
+      <c r="M299" s="0" t="n">
         <v>0.0702</v>
       </c>
-      <c r="N299" t="n">
+      <c r="N299" s="0" t="n">
         <v>0.0077</v>
       </c>
-      <c r="O299" t="inlineStr">
+      <c r="O299" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B300" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C300" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D300" t="n">
+      <c r="D300" s="0" t="n">
         <v>14500</v>
       </c>
-      <c r="E300" t="n">
+      <c r="E300" s="0" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F300" t="n">
+      <c r="F300" s="0" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G300" t="n">
+      <c r="G300" s="0" t="n">
         <v>13.792</v>
       </c>
-      <c r="H300" t="n">
+      <c r="H300" s="0" t="n">
         <v>-0.0072</v>
       </c>
-      <c r="I300" t="n">
+      <c r="I300" s="0" t="n">
         <v>199984</v>
       </c>
-      <c r="J300" t="n">
+      <c r="J300" s="0" t="n">
         <v>-1049.8</v>
       </c>
-      <c r="K300" t="n">
+      <c r="K300" s="0" t="n">
         <v>-0.0052</v>
       </c>
-      <c r="L300" t="n">
+      <c r="L300" s="0" t="n">
         <v>0.125</v>
       </c>
-      <c r="M300" t="n">
+      <c r="M300" s="0" t="n">
         <v>0.0596</v>
       </c>
-      <c r="N300" t="n">
+      <c r="N300" s="0" t="n">
         <v>-0.0654</v>
       </c>
-      <c r="O300" t="inlineStr">
+      <c r="O300" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C301" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D301" t="n">
+      <c r="D301" s="0" t="n">
         <v>3700</v>
       </c>
-      <c r="E301" t="n">
+      <c r="E301" s="0" t="n">
         <v>135.645</v>
       </c>
-      <c r="F301" t="n">
+      <c r="F301" s="0" t="n">
         <v>501886.5</v>
       </c>
-      <c r="G301" t="n">
+      <c r="G301" s="0" t="n">
         <v>134.796</v>
       </c>
-      <c r="H301" t="n">
+      <c r="H301" s="0" t="n">
         <v>0.0004</v>
       </c>
-      <c r="I301" t="n">
+      <c r="I301" s="0" t="n">
         <v>498745.2</v>
       </c>
-      <c r="J301" t="n">
+      <c r="J301" s="0" t="n">
         <v>-3141.3</v>
       </c>
-      <c r="K301" t="n">
+      <c r="K301" s="0" t="n">
         <v>-0.0063</v>
       </c>
-      <c r="L301" t="n">
+      <c r="L301" s="0" t="n">
         <v>0.125</v>
       </c>
-      <c r="M301" t="n">
+      <c r="M301" s="0" t="n">
         <v>0.1486</v>
       </c>
-      <c r="N301" t="n">
+      <c r="N301" s="0" t="n">
         <v>0.0236</v>
       </c>
-      <c r="O301" t="inlineStr">
+      <c r="O301" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B302" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C302" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D302" t="n">
+      <c r="D302" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="E302" t="n">
+      <c r="E302" s="0" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F302" t="n">
+      <c r="F302" s="0" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G302" t="n">
+      <c r="G302" s="0" t="n">
         <v>140.721</v>
       </c>
-      <c r="H302" t="n">
+      <c r="H302" s="0" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="I302" t="n">
+      <c r="I302" s="0" t="n">
         <v>492523.5</v>
       </c>
-      <c r="J302" t="n">
+      <c r="J302" s="0" t="n">
         <v>-1718.85</v>
       </c>
-      <c r="K302" t="n">
+      <c r="K302" s="0" t="n">
         <v>-0.0035</v>
       </c>
-      <c r="L302" t="n">
+      <c r="L302" s="0" t="n">
         <v>0.125</v>
       </c>
-      <c r="M302" t="n">
+      <c r="M302" s="0" t="n">
         <v>0.1467</v>
       </c>
-      <c r="N302" t="n">
+      <c r="N302" s="0" t="n">
         <v>0.0217</v>
       </c>
-      <c r="O302" t="inlineStr">
+      <c r="O302" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B303" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C303" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D303" t="n">
+      <c r="D303" s="0" t="n">
         <v>2200</v>
       </c>
-      <c r="E303" t="n">
+      <c r="E303" s="0" t="n">
         <v>113.462</v>
       </c>
-      <c r="F303" t="n">
+      <c r="F303" s="0" t="n">
         <v>249616.4</v>
       </c>
-      <c r="G303" t="n">
+      <c r="G303" s="0" t="n">
         <v>113.596</v>
       </c>
-      <c r="H303" t="n">
+      <c r="H303" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I303" t="n">
+      <c r="I303" s="0" t="n">
         <v>249911.2</v>
       </c>
-      <c r="J303" t="n">
+      <c r="J303" s="0" t="n">
         <v>294.8</v>
       </c>
-      <c r="K303" t="n">
+      <c r="K303" s="0" t="n">
         <v>0.0012</v>
       </c>
-      <c r="L303" t="n">
+      <c r="L303" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M303" t="n">
+      <c r="M303" s="0" t="n">
         <v>0.07439999999999999</v>
       </c>
-      <c r="N303" t="n">
+      <c r="N303" s="0" t="n">
         <v>0.0119</v>
       </c>
-      <c r="O303" t="inlineStr">
+      <c r="O303" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="0" t="inlineStr">
         <is>
           <t>20260626</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B304" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C304" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D304" t="n">
+      <c r="D304" s="0" t="n">
         <v>63800</v>
       </c>
-      <c r="E304" t="n">
+      <c r="E304" s="0" t="n">
         <v>9.1196</v>
       </c>
-      <c r="F304" t="n">
+      <c r="F304" s="0" t="n">
         <v>581830.48</v>
       </c>
-      <c r="G304" t="n">
+      <c r="G304" s="0" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="H304" t="n">
+      <c r="H304" s="0" t="n">
         <v>0.0124</v>
       </c>
-      <c r="I304" t="n">
+      <c r="I304" s="0" t="n">
         <v>535282</v>
       </c>
-      <c r="J304" t="n">
+      <c r="J304" s="0" t="n">
         <v>-46548.48</v>
       </c>
-      <c r="K304" t="n">
+      <c r="K304" s="0" t="n">
         <v>-0.08</v>
       </c>
-      <c r="L304" t="n">
+      <c r="L304" s="0" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M304" t="n">
+      <c r="M304" s="0" t="n">
         <v>0.1595</v>
       </c>
-      <c r="N304" t="n">
+      <c r="N304" s="0" t="n">
         <v>-0.028</v>
       </c>
-      <c r="O304" t="inlineStr">
+      <c r="O304" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -19834,4 +19948,845 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="1" min="1" max="1"/>
+    <col width="22" customWidth="1" style="1" min="2" max="2"/>
+    <col width="22" customWidth="1" style="1" min="3" max="3"/>
+    <col width="22" customWidth="1" style="1" min="4" max="4"/>
+    <col width="22" customWidth="1" style="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1" s="1">
+      <c r="A1" s="93" t="inlineStr">
+        <is>
+          <t>GA最优方案 — 遗传算法（达尔文优化）结果存档</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="94" t="inlineStr">
+        <is>
+          <t>一、四方案参数对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="95" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="B4" s="95" t="inlineStr">
+        <is>
+          <t>当前V3</t>
+        </is>
+      </c>
+      <c r="C4" s="95" t="inlineStr">
+        <is>
+          <t>GA最优</t>
+        </is>
+      </c>
+      <c r="D4" s="95" t="inlineStr">
+        <is>
+          <t>网格最佳</t>
+        </is>
+      </c>
+      <c r="E4" s="95" t="inlineStr">
+        <is>
+          <t>买入持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>止盈触发</t>
+        </is>
+      </c>
+      <c r="B5" s="96" t="inlineStr">
+        <is>
+          <t>+20%卖半</t>
+        </is>
+      </c>
+      <c r="C5" s="97" t="inlineStr">
+        <is>
+          <t>+5.1%全卖</t>
+        </is>
+      </c>
+      <c r="D5" s="96" t="inlineStr">
+        <is>
+          <t>+30%卖半</t>
+        </is>
+      </c>
+      <c r="E5" s="96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="96" t="inlineStr">
+        <is>
+          <t>止损触发</t>
+        </is>
+      </c>
+      <c r="B6" s="96" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="C6" s="97" t="inlineStr">
+        <is>
+          <t>-19.9%</t>
+        </is>
+      </c>
+      <c r="D6" s="96" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E6" s="96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>观察期</t>
+        </is>
+      </c>
+      <c r="B7" s="96" t="inlineStr">
+        <is>
+          <t>20交易日</t>
+        </is>
+      </c>
+      <c r="C7" s="97" t="inlineStr">
+        <is>
+          <t>32交易日</t>
+        </is>
+      </c>
+      <c r="D7" s="96" t="inlineStr">
+        <is>
+          <t>40交易日</t>
+        </is>
+      </c>
+      <c r="E7" s="96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="96" t="inlineStr">
+        <is>
+          <t>再平衡频率</t>
+        </is>
+      </c>
+      <c r="B8" s="96" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C8" s="97" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="D8" s="96" t="inlineStr">
+        <is>
+          <t>半年度</t>
+        </is>
+      </c>
+      <c r="E8" s="96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="96" t="inlineStr">
+        <is>
+          <t>再平衡阈值</t>
+        </is>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
+          <t>±20%</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="inlineStr">
+        <is>
+          <t>±28%</t>
+        </is>
+      </c>
+      <c r="D9" s="96" t="inlineStr">
+        <is>
+          <t>±10%</t>
+        </is>
+      </c>
+      <c r="E9" s="96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>二、回测指标对比（2021-2025，400万）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="95" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>当前V3</t>
+        </is>
+      </c>
+      <c r="C12" s="95" t="inlineStr">
+        <is>
+          <t>GA最优</t>
+        </is>
+      </c>
+      <c r="D12" s="95" t="inlineStr">
+        <is>
+          <t>网格最佳</t>
+        </is>
+      </c>
+      <c r="E12" s="95" t="inlineStr">
+        <is>
+          <t>买入持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="96" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
+        <is>
+          <t>+5.39%</t>
+        </is>
+      </c>
+      <c r="C13" s="97" t="inlineStr">
+        <is>
+          <t>+7.00%</t>
+        </is>
+      </c>
+      <c r="D13" s="96" t="inlineStr">
+        <is>
+          <t>+4.49%</t>
+        </is>
+      </c>
+      <c r="E13" s="96" t="inlineStr">
+        <is>
+          <t>+5.81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="96" t="inlineStr">
+        <is>
+          <t>总收益</t>
+        </is>
+      </c>
+      <c r="B14" s="96" t="inlineStr">
+        <is>
+          <t>+28.72%</t>
+        </is>
+      </c>
+      <c r="C14" s="97" t="inlineStr">
+        <is>
+          <t>+38.47%</t>
+        </is>
+      </c>
+      <c r="D14" s="96" t="inlineStr">
+        <is>
+          <t>+24.50%</t>
+        </is>
+      </c>
+      <c r="E14" s="96" t="inlineStr">
+        <is>
+          <t>+32.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="96" t="inlineStr">
+        <is>
+          <t>最大回撤</t>
+        </is>
+      </c>
+      <c r="B15" s="96" t="inlineStr">
+        <is>
+          <t>-10.32%</t>
+        </is>
+      </c>
+      <c r="C15" s="97" t="inlineStr">
+        <is>
+          <t>-8.89%</t>
+        </is>
+      </c>
+      <c r="D15" s="96" t="inlineStr">
+        <is>
+          <t>-7.96%</t>
+        </is>
+      </c>
+      <c r="E15" s="96" t="inlineStr">
+        <is>
+          <t>-12.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="96" t="inlineStr">
+        <is>
+          <t>夏普比率</t>
+        </is>
+      </c>
+      <c r="B16" s="96" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="C16" s="97" t="inlineStr">
+        <is>
+          <t>1.037</t>
+        </is>
+      </c>
+      <c r="D16" s="96" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="E16" s="96" t="inlineStr">
+        <is>
+          <t>0.802</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="96" t="inlineStr">
+        <is>
+          <t>最终净值</t>
+        </is>
+      </c>
+      <c r="B17" s="96" t="inlineStr">
+        <is>
+          <t>5,148,903</t>
+        </is>
+      </c>
+      <c r="C17" s="97" t="inlineStr">
+        <is>
+          <t>5,538,852</t>
+        </is>
+      </c>
+      <c r="D17" s="96" t="inlineStr">
+        <is>
+          <t>4,980,098</t>
+        </is>
+      </c>
+      <c r="E17" s="96" t="inlineStr">
+        <is>
+          <t>5,306,710</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="96" t="inlineStr">
+        <is>
+          <t>交易笔数</t>
+        </is>
+      </c>
+      <c r="B18" s="96" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C18" s="97" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D18" s="96" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E18" s="96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>三、逐年组合收益对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>当前V3</t>
+        </is>
+      </c>
+      <c r="C21" s="95" t="inlineStr">
+        <is>
+          <t>GA最优</t>
+        </is>
+      </c>
+      <c r="D21" s="95" t="inlineStr">
+        <is>
+          <t>网格最佳</t>
+        </is>
+      </c>
+      <c r="E21" s="95" t="inlineStr">
+        <is>
+          <t>买入持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="96" t="inlineStr">
+        <is>
+          <t>2021年</t>
+        </is>
+      </c>
+      <c r="B22" s="96" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="C22" s="97" t="inlineStr">
+        <is>
+          <t>+4.3%</t>
+        </is>
+      </c>
+      <c r="D22" s="96" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+      <c r="E22" s="96" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="96" t="inlineStr">
+        <is>
+          <t>2022年</t>
+        </is>
+      </c>
+      <c r="B23" s="96" t="inlineStr">
+        <is>
+          <t>-6.4%</t>
+        </is>
+      </c>
+      <c r="C23" s="97" t="inlineStr">
+        <is>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D23" s="96" t="inlineStr">
+        <is>
+          <t>-4.4%</t>
+        </is>
+      </c>
+      <c r="E23" s="96" t="inlineStr">
+        <is>
+          <t>-6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="96" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="B24" s="96" t="inlineStr">
+        <is>
+          <t>+0.8%</t>
+        </is>
+      </c>
+      <c r="C24" s="97" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="D24" s="96" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E24" s="96" t="inlineStr">
+        <is>
+          <t>+2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="96" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="B25" s="96" t="inlineStr">
+        <is>
+          <t>+11.4%</t>
+        </is>
+      </c>
+      <c r="C25" s="97" t="inlineStr">
+        <is>
+          <t>+13.4%</t>
+        </is>
+      </c>
+      <c r="D25" s="96" t="inlineStr">
+        <is>
+          <t>+27.0%</t>
+        </is>
+      </c>
+      <c r="E25" s="96" t="inlineStr">
+        <is>
+          <t>+13.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="96" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="B26" s="96" t="inlineStr">
+        <is>
+          <t>+21.6%</t>
+        </is>
+      </c>
+      <c r="C26" s="97" t="inlineStr">
+        <is>
+          <t>+22.0%</t>
+        </is>
+      </c>
+      <c r="D26" s="96" t="inlineStr">
+        <is>
+          <t>+19.3%</t>
+        </is>
+      </c>
+      <c r="E26" s="96" t="inlineStr">
+        <is>
+          <t>+23.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="96" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="B27" s="96" t="inlineStr">
+        <is>
+          <t>+5.2%</t>
+        </is>
+      </c>
+      <c r="C27" s="97" t="inlineStr">
+        <is>
+          <t>+6.7%</t>
+        </is>
+      </c>
+      <c r="D27" s="96" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="E27" s="96" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="98" t="inlineStr">
+        <is>
+          <t>四、GA最优方案详细参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="99" t="inlineStr">
+        <is>
+          <t>止盈触发 (sp_trigger)</t>
+        </is>
+      </c>
+      <c r="B30" s="96" t="inlineStr">
+        <is>
+          <t>&gt;= +5.1%</t>
+        </is>
+      </c>
+      <c r="C30" s="103" t="n"/>
+      <c r="D30" s="103" t="n"/>
+      <c r="E30" s="104" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="99" t="inlineStr">
+        <is>
+          <t>止盈卖出比例 (sp_sell_ratio)</t>
+        </is>
+      </c>
+      <c r="B31" s="96" t="inlineStr">
+        <is>
+          <t>100%（全部卖出）</t>
+        </is>
+      </c>
+      <c r="C31" s="103" t="n"/>
+      <c r="D31" s="103" t="n"/>
+      <c r="E31" s="104" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="99" t="inlineStr">
+        <is>
+          <t>止损触发 (sl_trigger)</t>
+        </is>
+      </c>
+      <c r="B32" s="96" t="inlineStr">
+        <is>
+          <t>&lt;= -19.9%（实操约-20%）</t>
+        </is>
+      </c>
+      <c r="C32" s="103" t="n"/>
+      <c r="D32" s="103" t="n"/>
+      <c r="E32" s="104" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="99" t="inlineStr">
+        <is>
+          <t>观察期 (observe_days)</t>
+        </is>
+      </c>
+      <c r="B33" s="96" t="inlineStr">
+        <is>
+          <t>32个交易日（约45自然日）</t>
+        </is>
+      </c>
+      <c r="C33" s="103" t="n"/>
+      <c r="D33" s="103" t="n"/>
+      <c r="E33" s="104" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="99" t="inlineStr">
+        <is>
+          <t>再平衡频率 (rb_freq)</t>
+        </is>
+      </c>
+      <c r="B34" s="96" t="inlineStr">
+        <is>
+          <t>年度（12月末）</t>
+        </is>
+      </c>
+      <c r="C34" s="103" t="n"/>
+      <c r="D34" s="103" t="n"/>
+      <c r="E34" s="104" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="99" t="inlineStr">
+        <is>
+          <t>再平衡阈值 (rb_threshold)</t>
+        </is>
+      </c>
+      <c r="B35" s="96" t="inlineStr">
+        <is>
+          <t>偏离&gt;=±28%触发</t>
+        </is>
+      </c>
+      <c r="C35" s="103" t="n"/>
+      <c r="D35" s="103" t="n"/>
+      <c r="E35" s="104" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="99" t="inlineStr">
+        <is>
+          <t>回测CAGR</t>
+        </is>
+      </c>
+      <c r="B36" s="96" t="inlineStr">
+        <is>
+          <t>+7.00%</t>
+        </is>
+      </c>
+      <c r="C36" s="103" t="n"/>
+      <c r="D36" s="103" t="n"/>
+      <c r="E36" s="104" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="99" t="inlineStr">
+        <is>
+          <t>累计收益</t>
+        </is>
+      </c>
+      <c r="B37" s="96" t="inlineStr">
+        <is>
+          <t>+38.47%（400万→553.9万）</t>
+        </is>
+      </c>
+      <c r="C37" s="103" t="n"/>
+      <c r="D37" s="103" t="n"/>
+      <c r="E37" s="104" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="99" t="inlineStr">
+        <is>
+          <t>最大回撤</t>
+        </is>
+      </c>
+      <c r="B38" s="96" t="inlineStr">
+        <is>
+          <t>-8.89%</t>
+        </is>
+      </c>
+      <c r="C38" s="103" t="n"/>
+      <c r="D38" s="103" t="n"/>
+      <c r="E38" s="104" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="99" t="inlineStr">
+        <is>
+          <t>夏普比率</t>
+        </is>
+      </c>
+      <c r="B39" s="96" t="inlineStr">
+        <is>
+          <t>1.037</t>
+        </is>
+      </c>
+      <c r="C39" s="103" t="n"/>
+      <c r="D39" s="103" t="n"/>
+      <c r="E39" s="104" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="99" t="inlineStr">
+        <is>
+          <t>总交易笔数</t>
+        </is>
+      </c>
+      <c r="B40" s="96" t="inlineStr">
+        <is>
+          <t>66笔</t>
+        </is>
+      </c>
+      <c r="C40" s="103" t="n"/>
+      <c r="D40" s="103" t="n"/>
+      <c r="E40" s="104" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="99" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="B41" s="96" t="inlineStr">
+        <is>
+          <t>当前按V3执行，正式迁移时参考此方案</t>
+        </is>
+      </c>
+      <c r="C41" s="103" t="n"/>
+      <c r="D41" s="103" t="n"/>
+      <c r="E41" s="104" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="101" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="102" t="inlineStr">
+        <is>
+          <t>1. 回测区间：2021-01-01 ~ 2025-12-31，初始400万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="102" t="inlineStr">
+        <is>
+          <t>2. 由遗传算法(60个体x50代=3000次回测)搜索得到</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="102" t="inlineStr">
+        <is>
+          <t>3. 当前仍按V3方案执行，GA方案仅存档备查</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="102" t="inlineStr">
+        <is>
+          <t>4. 后续如需切换，需同步修改update_portfolio.py中的信号检测规则</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B34:E34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/400万资产配置组合2026.xlsx
+++ b/400万资产配置组合2026.xlsx
@@ -2381,7 +2381,7 @@
     <row r="1" ht="115.2" customHeight="1" s="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>更新日期: 2026-06-27 (数据日期: 2026-06-26)</t>
+          <t>更新日期: 2026-07-01 (数据日期: 2026-07-01)</t>
         </is>
       </c>
       <c r="B1" s="16" t="inlineStr">
@@ -2475,10 +2475,10 @@
         <v>0.1875</v>
       </c>
       <c r="F2" s="71" t="n">
-        <v>0.2248</v>
+        <v>0.2274</v>
       </c>
       <c r="G2" s="71" t="n">
-        <v>0.0373</v>
+        <v>0.0399</v>
       </c>
       <c r="H2" s="72" t="n">
         <v>4.885</v>
@@ -2491,13 +2491,13 @@
         <v/>
       </c>
       <c r="K2" s="75" t="n">
-        <v>4.907</v>
+        <v>5.019</v>
       </c>
       <c r="L2" s="76" t="n">
-        <v>3383.6</v>
+        <v>20609.2</v>
       </c>
       <c r="M2" s="77" t="n">
-        <v>0.0045</v>
+        <v>0.0274</v>
       </c>
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="78" t="n"/>
@@ -2527,10 +2527,10 @@
         <v>0.0625</v>
       </c>
       <c r="F3" s="81" t="n">
-        <v>0.0371</v>
+        <v>0.0402</v>
       </c>
       <c r="G3" s="81" t="n">
-        <v>-0.0254</v>
+        <v>-0.0223</v>
       </c>
       <c r="H3" s="82" t="n">
         <v>1.838</v>
@@ -2543,15 +2543,19 @@
         <v/>
       </c>
       <c r="K3" s="85" t="n">
-        <v>2.077</v>
+        <v>2.277</v>
       </c>
       <c r="L3" s="86" t="n">
-        <v>14340</v>
+        <v>26340</v>
       </c>
       <c r="M3" s="68" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="N3" s="4" t="n"/>
+        <v>0.2388</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>🟢V3止盈：浮盈23.9% &gt;= +20%，卖半仓，资金转入511360短融ETF</t>
+        </is>
+      </c>
       <c r="O3" s="78" t="inlineStr">
         <is>
           <t>42,600份(部分建仓)</t>
@@ -2581,10 +2585,10 @@
         <v>0.0625</v>
       </c>
       <c r="F4" s="71" t="n">
-        <v>0.0791</v>
+        <v>0.081</v>
       </c>
       <c r="G4" s="71" t="n">
-        <v>0.0166</v>
+        <v>0.0185</v>
       </c>
       <c r="H4" s="75" t="n">
         <v>3.968</v>
@@ -2597,13 +2601,13 @@
         <v/>
       </c>
       <c r="K4" s="85" t="n">
-        <v>4.215</v>
+        <v>4.364</v>
       </c>
       <c r="L4" s="76" t="n">
-        <v>15561</v>
+        <v>24948</v>
       </c>
       <c r="M4" s="77" t="n">
-        <v>0.0622</v>
+        <v>0.0998</v>
       </c>
       <c r="N4" s="23" t="n"/>
       <c r="O4" s="78" t="inlineStr">
@@ -2632,10 +2636,10 @@
         <v>0.0625</v>
       </c>
       <c r="F5" s="71" t="n">
-        <v>0.0702</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="G5" s="71" t="n">
-        <v>0.0077</v>
+        <v>0.006</v>
       </c>
       <c r="H5" s="75" t="n">
         <v>1.15</v>
@@ -2648,13 +2652,13 @@
         <v/>
       </c>
       <c r="K5" s="85" t="n">
-        <v>1.081</v>
+        <v>1.067</v>
       </c>
       <c r="L5" s="76" t="n">
-        <v>-15042</v>
+        <v>-18094</v>
       </c>
       <c r="M5" s="77" t="n">
-        <v>-0.06</v>
+        <v>-0.0722</v>
       </c>
       <c r="N5" s="23" t="n"/>
       <c r="O5" s="78" t="n"/>
@@ -2695,13 +2699,13 @@
         <v/>
       </c>
       <c r="K6" s="82" t="n">
-        <v>13.792</v>
+        <v>13.954</v>
       </c>
       <c r="L6" s="86" t="n">
-        <v>-1049.8</v>
+        <v>1299.2</v>
       </c>
       <c r="M6" s="68" t="n">
-        <v>-0.0052</v>
+        <v>0.0065</v>
       </c>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="78">
@@ -2729,10 +2733,10 @@
         <v>0.125</v>
       </c>
       <c r="F7" s="71" t="n">
-        <v>0.1486</v>
+        <v>0.147</v>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.0236</v>
+        <v>0.022</v>
       </c>
       <c r="H7" s="75" t="n">
         <v>135.645</v>
@@ -2745,13 +2749,13 @@
         <v/>
       </c>
       <c r="K7" s="85" t="n">
-        <v>134.796</v>
+        <v>134.854</v>
       </c>
       <c r="L7" s="76" t="n">
-        <v>-3141.3</v>
+        <v>-2926.7</v>
       </c>
       <c r="M7" s="77" t="n">
-        <v>-0.0063</v>
+        <v>-0.0058</v>
       </c>
       <c r="N7" s="23" t="n"/>
       <c r="O7" s="78" t="n"/>
@@ -2776,10 +2780,10 @@
         <v>0.125</v>
       </c>
       <c r="F8" s="71" t="n">
-        <v>0.1467</v>
+        <v>0.1452</v>
       </c>
       <c r="G8" s="71" t="n">
-        <v>0.0217</v>
+        <v>0.0202</v>
       </c>
       <c r="H8" s="75" t="n">
         <v>141.2121</v>
@@ -2792,13 +2796,13 @@
         <v/>
       </c>
       <c r="K8" s="85" t="n">
-        <v>140.721</v>
+        <v>140.792</v>
       </c>
       <c r="L8" s="76" t="n">
-        <v>-1718.85</v>
+        <v>-1470.35</v>
       </c>
       <c r="M8" s="77" t="n">
-        <v>-0.0035</v>
+        <v>-0.003</v>
       </c>
       <c r="N8" s="23" t="n"/>
       <c r="O8" s="78" t="n"/>
@@ -2823,10 +2827,10 @@
         <v>0.0625</v>
       </c>
       <c r="F9" s="71" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0736</v>
       </c>
       <c r="G9" s="71" t="n">
-        <v>0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H9" s="75" t="n">
         <v>113.462</v>
@@ -2839,13 +2843,13 @@
         <v/>
       </c>
       <c r="K9" s="85" t="n">
-        <v>113.596</v>
+        <v>113.61</v>
       </c>
       <c r="L9" s="76" t="n">
-        <v>294.8</v>
+        <v>325.6</v>
       </c>
       <c r="M9" s="77" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="N9" s="23" t="n"/>
       <c r="O9" s="78" t="n"/>
@@ -2870,10 +2874,10 @@
         <v>0.1875</v>
       </c>
       <c r="F10" s="81" t="n">
-        <v>0.1595</v>
+        <v>0.1575</v>
       </c>
       <c r="G10" s="81" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="H10" s="87" t="n">
         <v>9.1196</v>
@@ -2886,13 +2890,13 @@
         <v/>
       </c>
       <c r="K10" s="85" t="n">
-        <v>8.390000000000001</v>
+        <v>8.378</v>
       </c>
       <c r="L10" s="86" t="n">
-        <v>-46548.48</v>
+        <v>-47314.08</v>
       </c>
       <c r="M10" s="68" t="n">
-        <v>-0.08</v>
+        <v>-0.0813</v>
       </c>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="78">
@@ -3644,7 +3648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q231"/>
+  <dimension ref="A1:Q258"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="11.8181818181818" customWidth="1" style="1" min="1" max="1"/>
@@ -16380,6 +16384,1479 @@
         <v>-0.028</v>
       </c>
       <c r="O231" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="D232" s="0" t="n">
+        <v>153800</v>
+      </c>
+      <c r="E232" s="0" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="F232" s="0" t="n">
+        <v>751313</v>
+      </c>
+      <c r="G232" s="0" t="n">
+        <v>4.959</v>
+      </c>
+      <c r="H232" s="0" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="I232" s="0" t="n">
+        <v>762694.2</v>
+      </c>
+      <c r="J232" s="0" t="n">
+        <v>11381.2</v>
+      </c>
+      <c r="K232" s="0" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="L232" s="0" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M232" s="0" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="N232" s="0" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="O232" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>588050</t>
+        </is>
+      </c>
+      <c r="D233" s="0" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E233" s="0" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="F233" s="0" t="n">
+        <v>110280</v>
+      </c>
+      <c r="G233" s="0" t="n">
+        <v>2.182</v>
+      </c>
+      <c r="H233" s="0" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="I233" s="0" t="n">
+        <v>130920</v>
+      </c>
+      <c r="J233" s="0" t="n">
+        <v>20640</v>
+      </c>
+      <c r="K233" s="0" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="L233" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M233" s="0" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="N233" s="0" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="O233" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B234" s="0" t="inlineStr">
+        <is>
+          <t>创业板ETF</t>
+        </is>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="D234" s="0" t="n">
+        <v>63000</v>
+      </c>
+      <c r="E234" s="0" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="F234" s="0" t="n">
+        <v>249984</v>
+      </c>
+      <c r="G234" s="0" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="H234" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I234" s="0" t="n">
+        <v>266868</v>
+      </c>
+      <c r="J234" s="0" t="n">
+        <v>16884</v>
+      </c>
+      <c r="K234" s="0" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="L234" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M234" s="0" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="N234" s="0" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="O234" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>红利低波ETF</t>
+        </is>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="D235" s="0" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E235" s="0" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F235" s="0" t="n">
+        <v>250700</v>
+      </c>
+      <c r="G235" s="0" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="H235" s="0" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="I235" s="0" t="n">
+        <v>237402</v>
+      </c>
+      <c r="J235" s="0" t="n">
+        <v>-13298</v>
+      </c>
+      <c r="K235" s="0" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="L235" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M235" s="0" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="N235" s="0" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="O235" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E236" s="0" t="n">
+        <v>13.8644</v>
+      </c>
+      <c r="F236" s="0" t="n">
+        <v>201033.8</v>
+      </c>
+      <c r="G236" s="0" t="n">
+        <v>13.792</v>
+      </c>
+      <c r="I236" s="0" t="n">
+        <v>199984</v>
+      </c>
+      <c r="J236" s="0" t="n">
+        <v>-1049.8</v>
+      </c>
+      <c r="K236" s="0" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="L236" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M236" s="0" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="N236" s="0" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="O236" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t>10年国债ETF</t>
+        </is>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>511260</t>
+        </is>
+      </c>
+      <c r="D237" s="0" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E237" s="0" t="n">
+        <v>135.645</v>
+      </c>
+      <c r="F237" s="0" t="n">
+        <v>501886.5</v>
+      </c>
+      <c r="G237" s="0" t="n">
+        <v>134.97</v>
+      </c>
+      <c r="H237" s="0" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="I237" s="0" t="n">
+        <v>499389</v>
+      </c>
+      <c r="J237" s="0" t="n">
+        <v>-2497.5</v>
+      </c>
+      <c r="K237" s="0" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L237" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M237" s="0" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="N237" s="0" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="O237" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B238" s="0" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="D238" s="0" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E238" s="0" t="n">
+        <v>141.2121</v>
+      </c>
+      <c r="F238" s="0" t="n">
+        <v>494242.35</v>
+      </c>
+      <c r="G238" s="0" t="n">
+        <v>140.845</v>
+      </c>
+      <c r="H238" s="0" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="I238" s="0" t="n">
+        <v>492957.5</v>
+      </c>
+      <c r="J238" s="0" t="n">
+        <v>-1284.85</v>
+      </c>
+      <c r="K238" s="0" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="L238" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M238" s="0" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="N238" s="0" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="O238" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B239" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="D239" s="0" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E239" s="0" t="n">
+        <v>113.462</v>
+      </c>
+      <c r="F239" s="0" t="n">
+        <v>249616.4</v>
+      </c>
+      <c r="G239" s="0" t="n">
+        <v>113.597</v>
+      </c>
+      <c r="I239" s="0" t="n">
+        <v>249913.4</v>
+      </c>
+      <c r="J239" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="K239" s="0" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="L239" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M239" s="0" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="N239" s="0" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="O239" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B240" s="0" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="D240" s="0" t="n">
+        <v>63800</v>
+      </c>
+      <c r="E240" s="0" t="n">
+        <v>9.1196</v>
+      </c>
+      <c r="F240" s="0" t="n">
+        <v>581830.48</v>
+      </c>
+      <c r="G240" s="0" t="n">
+        <v>8.449</v>
+      </c>
+      <c r="H240" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I240" s="0" t="n">
+        <v>539046.2</v>
+      </c>
+      <c r="J240" s="0" t="n">
+        <v>-42784.28</v>
+      </c>
+      <c r="K240" s="0" t="n">
+        <v>-0.0735</v>
+      </c>
+      <c r="L240" s="0" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M240" s="0" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="N240" s="0" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="O240" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="D241" s="0" t="n">
+        <v>153800</v>
+      </c>
+      <c r="E241" s="0" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="F241" s="0" t="n">
+        <v>751313</v>
+      </c>
+      <c r="G241" s="0" t="n">
+        <v>4.959</v>
+      </c>
+      <c r="H241" s="0" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="I241" s="0" t="n">
+        <v>762694.2</v>
+      </c>
+      <c r="J241" s="0" t="n">
+        <v>11381.2</v>
+      </c>
+      <c r="K241" s="0" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="L241" s="0" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M241" s="0" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="N241" s="0" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="O241" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B242" s="0" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>588050</t>
+        </is>
+      </c>
+      <c r="D242" s="0" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E242" s="0" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="F242" s="0" t="n">
+        <v>110280</v>
+      </c>
+      <c r="G242" s="0" t="n">
+        <v>2.182</v>
+      </c>
+      <c r="H242" s="0" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="I242" s="0" t="n">
+        <v>130920</v>
+      </c>
+      <c r="J242" s="0" t="n">
+        <v>20640</v>
+      </c>
+      <c r="K242" s="0" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="L242" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M242" s="0" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="N242" s="0" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="O242" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B243" s="0" t="inlineStr">
+        <is>
+          <t>创业板ETF</t>
+        </is>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="D243" s="0" t="n">
+        <v>63000</v>
+      </c>
+      <c r="E243" s="0" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="F243" s="0" t="n">
+        <v>249984</v>
+      </c>
+      <c r="G243" s="0" t="n">
+        <v>4.236</v>
+      </c>
+      <c r="H243" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I243" s="0" t="n">
+        <v>266868</v>
+      </c>
+      <c r="J243" s="0" t="n">
+        <v>16884</v>
+      </c>
+      <c r="K243" s="0" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="L243" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M243" s="0" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="N243" s="0" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="O243" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t>红利低波ETF</t>
+        </is>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="D244" s="0" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E244" s="0" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F244" s="0" t="n">
+        <v>250700</v>
+      </c>
+      <c r="G244" s="0" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="H244" s="0" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="I244" s="0" t="n">
+        <v>237402</v>
+      </c>
+      <c r="J244" s="0" t="n">
+        <v>-13298</v>
+      </c>
+      <c r="K244" s="0" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="L244" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M244" s="0" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="N244" s="0" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="O244" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E245" s="0" t="n">
+        <v>13.8644</v>
+      </c>
+      <c r="F245" s="0" t="n">
+        <v>201033.8</v>
+      </c>
+      <c r="G245" s="0" t="n">
+        <v>13.792</v>
+      </c>
+      <c r="I245" s="0" t="n">
+        <v>199984</v>
+      </c>
+      <c r="J245" s="0" t="n">
+        <v>-1049.8</v>
+      </c>
+      <c r="K245" s="0" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="L245" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M245" s="0" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="N245" s="0" t="n">
+        <v>-0.0658</v>
+      </c>
+      <c r="O245" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B246" s="0" t="inlineStr">
+        <is>
+          <t>10年国债ETF</t>
+        </is>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>511260</t>
+        </is>
+      </c>
+      <c r="D246" s="0" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E246" s="0" t="n">
+        <v>135.645</v>
+      </c>
+      <c r="F246" s="0" t="n">
+        <v>501886.5000000001</v>
+      </c>
+      <c r="G246" s="0" t="n">
+        <v>134.97</v>
+      </c>
+      <c r="H246" s="0" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="I246" s="0" t="n">
+        <v>499389</v>
+      </c>
+      <c r="J246" s="0" t="n">
+        <v>-2497.5</v>
+      </c>
+      <c r="K246" s="0" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L246" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M246" s="0" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="N246" s="0" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="O246" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E247" s="0" t="n">
+        <v>141.2121</v>
+      </c>
+      <c r="F247" s="0" t="n">
+        <v>494242.35</v>
+      </c>
+      <c r="G247" s="0" t="n">
+        <v>140.845</v>
+      </c>
+      <c r="H247" s="0" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="I247" s="0" t="n">
+        <v>492957.5</v>
+      </c>
+      <c r="J247" s="0" t="n">
+        <v>-1284.85</v>
+      </c>
+      <c r="K247" s="0" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="L247" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M247" s="0" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="N247" s="0" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="O247" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E248" s="0" t="n">
+        <v>113.462</v>
+      </c>
+      <c r="F248" s="0" t="n">
+        <v>249616.4</v>
+      </c>
+      <c r="G248" s="0" t="n">
+        <v>113.597</v>
+      </c>
+      <c r="I248" s="0" t="n">
+        <v>249913.4</v>
+      </c>
+      <c r="J248" s="0" t="n">
+        <v>297</v>
+      </c>
+      <c r="K248" s="0" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="L248" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M248" s="0" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="N248" s="0" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="O248" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="n">
+        <v>63800</v>
+      </c>
+      <c r="E249" s="0" t="n">
+        <v>9.1196</v>
+      </c>
+      <c r="F249" s="0" t="n">
+        <v>581830.48</v>
+      </c>
+      <c r="G249" s="0" t="n">
+        <v>8.449</v>
+      </c>
+      <c r="H249" s="0" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I249" s="0" t="n">
+        <v>539046.2</v>
+      </c>
+      <c r="J249" s="0" t="n">
+        <v>-42784.28</v>
+      </c>
+      <c r="K249" s="0" t="n">
+        <v>-0.0735</v>
+      </c>
+      <c r="L249" s="0" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M249" s="0" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="N249" s="0" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="O249" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>153800</v>
+      </c>
+      <c r="E250" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="F250" t="n">
+        <v>751313</v>
+      </c>
+      <c r="G250" t="n">
+        <v>5.019</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="I250" t="n">
+        <v>771922.2</v>
+      </c>
+      <c r="J250" t="n">
+        <v>20609.2</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="L250" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>588050</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="F251" t="n">
+        <v>110280</v>
+      </c>
+      <c r="G251" t="n">
+        <v>2.277</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="I251" t="n">
+        <v>136620</v>
+      </c>
+      <c r="J251" t="n">
+        <v>26340</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="N251" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>🟢V3止盈：浮盈23.9% &gt;= +20%，卖半仓，资金转入511360短融ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>创业板ETF</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>63000</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="F252" t="n">
+        <v>249984</v>
+      </c>
+      <c r="G252" t="n">
+        <v>4.364</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="I252" t="n">
+        <v>274932</v>
+      </c>
+      <c r="J252" t="n">
+        <v>24948</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>红利低波ETF</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F253" t="n">
+        <v>250700</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="H253" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="I253" t="n">
+        <v>232606</v>
+      </c>
+      <c r="J253" t="n">
+        <v>-18094</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-0.0722</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E254" t="n">
+        <v>13.8644</v>
+      </c>
+      <c r="F254" t="n">
+        <v>201033.8</v>
+      </c>
+      <c r="G254" t="n">
+        <v>13.954</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="I254" t="n">
+        <v>202333</v>
+      </c>
+      <c r="J254" t="n">
+        <v>1299.2</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="N254" t="n">
+        <v>-0.0654</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>10年国债ETF</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>511260</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E255" t="n">
+        <v>135.645</v>
+      </c>
+      <c r="F255" t="n">
+        <v>501886.5</v>
+      </c>
+      <c r="G255" t="n">
+        <v>134.854</v>
+      </c>
+      <c r="H255" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="I255" t="n">
+        <v>498959.8</v>
+      </c>
+      <c r="J255" t="n">
+        <v>-2926.7</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E256" t="n">
+        <v>141.2121</v>
+      </c>
+      <c r="F256" t="n">
+        <v>494242.35</v>
+      </c>
+      <c r="G256" t="n">
+        <v>140.792</v>
+      </c>
+      <c r="H256" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="I256" t="n">
+        <v>492772</v>
+      </c>
+      <c r="J256" t="n">
+        <v>-1470.35</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M256" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E257" t="n">
+        <v>113.462</v>
+      </c>
+      <c r="F257" t="n">
+        <v>249616.4</v>
+      </c>
+      <c r="G257" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I257" t="n">
+        <v>249942</v>
+      </c>
+      <c r="J257" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>63800</v>
+      </c>
+      <c r="E258" t="n">
+        <v>9.1196</v>
+      </c>
+      <c r="F258" t="n">
+        <v>581830.48</v>
+      </c>
+      <c r="G258" t="n">
+        <v>8.378</v>
+      </c>
+      <c r="H258" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="I258" t="n">
+        <v>534516.4</v>
+      </c>
+      <c r="J258" t="n">
+        <v>-47314.08</v>
+      </c>
+      <c r="K258" t="n">
+        <v>-0.0813</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M258" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="N258" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="O258" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/400万资产配置组合2026.xlsx
+++ b/400万资产配置组合2026.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GA优化方案" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'流水'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,25 +21,69 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="[$-409]yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="0.0000%"/>
-    <numFmt numFmtId="171" formatCode="0.000%"/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="0.0000%"/>
+    <numFmt numFmtId="172" formatCode="0.000%"/>
+    <numFmt numFmtId="173" formatCode="0.0000"/>
+    <numFmt numFmtId="174" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
+    <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="34">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -65,12 +109,6 @@
     <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
       <i val="1"/>
       <sz val="9"/>
     </font>
@@ -79,11 +117,6 @@
       <charset val="134"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
       <sz val="10"/>
     </font>
     <font>
@@ -241,43 +274,8 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -286,8 +284,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+        <bgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
     <fill>
@@ -298,8 +302,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
-        <bgColor rgb="FF2F5496"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -488,26 +492,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -519,6 +505,30 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -629,37 +639,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -682,141 +678,162 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -839,13 +856,14 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -854,129 +872,126 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -985,59 +1000,59 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1046,16 +1061,16 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1068,28 +1083,8 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="38" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1692,658 +1687,658 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>400万资产配置 -- 投资纪律速查（V3优化版 2026-06-27)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" s="1">
-      <c r="A3" s="47" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>一、单档止盈（+20%卖半）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="39" customHeight="1" s="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>适用：510300/588050/159915/512890/511380</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>不适用：债底</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14.5" customHeight="1" s="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>档位</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>浮盈阈值</t>
         </is>
       </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>减仓比例</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>锁定规则</t>
         </is>
       </c>
-      <c r="E5" s="51" t="n"/>
+      <c r="E5" s="63" t="n"/>
     </row>
     <row r="6" ht="14.5" customHeight="1" s="1">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>第一档</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>&gt;= +20%</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>仅触发一次，标记[已兑现]（重建后重置）</t>
         </is>
       </c>
-      <c r="E6" s="53" t="n"/>
+      <c r="E6" s="64" t="n"/>
     </row>
     <row r="7" ht="14.5" customHeight="1" s="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>【优化】止盈资金买入511360短融ETF，不临时再配置到其他品种，等待年度再平衡统一调配</t>
         </is>
       </c>
-      <c r="B7" s="53" t="n"/>
-      <c r="C7" s="53" t="n"/>
-      <c r="D7" s="53" t="n"/>
-      <c r="E7" s="53" t="n"/>
+      <c r="B7" s="64" t="n"/>
+      <c r="C7" s="64" t="n"/>
+      <c r="D7" s="64" t="n"/>
+      <c r="E7" s="64" t="n"/>
     </row>
     <row r="8" ht="14.5" customHeight="1" s="1">
-      <c r="A8" s="53" t="n"/>
-      <c r="B8" s="53" t="n"/>
-      <c r="C8" s="53" t="n"/>
-      <c r="D8" s="53" t="n"/>
-      <c r="E8" s="53" t="n"/>
+      <c r="A8" s="64" t="n"/>
+      <c r="B8" s="64" t="n"/>
+      <c r="C8" s="64" t="n"/>
+      <c r="D8" s="64" t="n"/>
+      <c r="E8" s="64" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" s="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>二、统一止损（-15%清仓，观察20日）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39" customHeight="1" s="1">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>适用：510300/588050/159915/512890/511380</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>不适用：债底（511260/511010/511360）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>档位</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>浮亏阈值</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>执行动作</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>后续规则</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="1">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>止损线</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>&gt;= -15%（较成本价）</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>当日或次日开盘市价卖出全部持仓</t>
         </is>
       </c>
-      <c r="D12" s="49" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>清仓后观察20个交易日方可重建（约1个月）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14.5" customHeight="1" s="1">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>【优化】取消高波动专用止损，执行统一规则；观察期40日→20日；取消动态止损预警</t>
         </is>
       </c>
-      <c r="B13" s="51" t="n"/>
-      <c r="C13" s="51" t="n"/>
-      <c r="D13" s="51" t="n"/>
-      <c r="E13" s="51" t="n"/>
+      <c r="B13" s="63" t="n"/>
+      <c r="C13" s="63" t="n"/>
+      <c r="D13" s="63" t="n"/>
+      <c r="E13" s="63" t="n"/>
     </row>
     <row r="14" ht="14.5" customHeight="1" s="1">
-      <c r="A14" s="53" t="n"/>
-      <c r="B14" s="53" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
-      <c r="E14" s="53" t="n"/>
+      <c r="A14" s="64" t="n"/>
+      <c r="B14" s="64" t="n"/>
+      <c r="C14" s="64" t="n"/>
+      <c r="D14" s="64" t="n"/>
+      <c r="E14" s="64" t="n"/>
     </row>
     <row r="15" ht="14.5" customHeight="1" s="1">
-      <c r="A15" s="52" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>三、组合再平衡（年度末 ±20% 阀值）</t>
         </is>
       </c>
-      <c r="B15" s="53" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
-      <c r="E15" s="53" t="n"/>
+      <c r="B15" s="64" t="n"/>
+      <c r="C15" s="64" t="n"/>
+      <c r="D15" s="64" t="n"/>
+      <c r="E15" s="64" t="n"/>
     </row>
     <row r="16" ht="14.5" customHeight="1" s="1">
-      <c r="A16" s="52" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>检查频率</t>
         </is>
       </c>
-      <c r="B16" s="52" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>阀值</t>
         </is>
       </c>
-      <c r="C16" s="52" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>执行动作</t>
         </is>
       </c>
-      <c r="D16" s="52" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>完成时限</t>
         </is>
       </c>
-      <c r="E16" s="53" t="n"/>
+      <c r="E16" s="64" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1" s="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr">
         <is>
           <t>年度末（12月最后交易日）</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>相对偏离 &gt; ±20%</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>全仓调回目标权重</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>当日收盘执行</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" s="1">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="65" t="inlineStr">
         <is>
           <t>偏离计算：(实际权重-目标权重)/目标权重</t>
         </is>
       </c>
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>例：目标10%→实际&lt;8%或&gt;12%触发</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" s="1">
-      <c r="A19" s="49" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>卖出排序：黄金&gt;科创/创业&gt;可转债&gt;沪深300&gt;红利低波</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="1">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>【优化】再平衡频率从半年度改为年度，降低摩擦成本，让利润充分奔跑</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="n"/>
+      <c r="A21" s="66" t="n"/>
       <c r="B21" s="0" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1" s="1">
-      <c r="A22" s="49" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>四、熔断与黑天鹅应对</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="1">
-      <c r="A23" s="47" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>档位</t>
         </is>
       </c>
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>组合回撤</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="61" t="inlineStr">
         <is>
           <t>触发状态</t>
         </is>
       </c>
-      <c r="D23" s="49" t="inlineStr">
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>强制动作</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.5" customHeight="1" s="1">
-      <c r="A24" s="50" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>绿色</t>
         </is>
       </c>
-      <c r="B24" s="50" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>&lt; -5%</t>
         </is>
       </c>
-      <c r="C24" s="50" t="inlineStr">
+      <c r="C24" s="62" t="inlineStr">
         <is>
           <t>正常波动</t>
         </is>
       </c>
-      <c r="D24" s="50" t="inlineStr">
+      <c r="D24" s="62" t="inlineStr">
         <is>
           <t>维持既有纪律</t>
         </is>
       </c>
-      <c r="E24" s="51" t="n"/>
+      <c r="E24" s="63" t="n"/>
     </row>
     <row r="25" ht="14.5" customHeight="1" s="1">
-      <c r="A25" s="52" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>黄色</t>
         </is>
       </c>
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>&gt;= -10%</t>
         </is>
       </c>
-      <c r="C25" s="52" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>组合预警</t>
         </is>
       </c>
-      <c r="D25" s="52" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>暂停新建仓+追涨，仅允许止盈/止损/再平衡</t>
         </is>
       </c>
-      <c r="E25" s="53" t="n"/>
+      <c r="E25" s="64" t="n"/>
     </row>
     <row r="26" ht="14.5" customHeight="1" s="1">
-      <c r="A26" s="52" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>红色</t>
         </is>
       </c>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>&gt;= -12%</t>
         </is>
       </c>
-      <c r="C26" s="52" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>组合熔断</t>
         </is>
       </c>
-      <c r="D26" s="52" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>权益压至60%以下，资金转债券/货基</t>
         </is>
       </c>
-      <c r="E26" s="53" t="n"/>
+      <c r="E26" s="64" t="n"/>
     </row>
     <row r="27" ht="14.5" customHeight="1" s="1">
-      <c r="A27" s="52" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>黑天鹅</t>
         </is>
       </c>
-      <c r="B27" s="52" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>&gt;= -15%</t>
         </is>
       </c>
-      <c r="C27" s="52" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>极端风险</t>
         </is>
       </c>
-      <c r="D27" s="52" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>权益压至40%以下；保留20%现金+40%债券</t>
         </is>
       </c>
-      <c r="E27" s="53" t="n"/>
+      <c r="E27" s="64" t="n"/>
     </row>
     <row r="28" ht="56" customHeight="1" s="1">
-      <c r="A28" s="49" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr">
         <is>
           <t>黑天鹅卖出顺序：科创50&gt;创业板&gt;黄金(保留底10万)&gt;可转债</t>
         </is>
       </c>
-      <c r="B28" s="49" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>恢复：回撤&lt;-10%</t>
         </is>
       </c>
     </row>
     <row r="29" ht="39" customHeight="1" s="1">
-      <c r="A29" s="54" t="inlineStr">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t>不可抗拒条款：触发当日必须下达卖出指令，不得以等反弹为由拖延</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="56" t="n"/>
+      <c r="A30" s="67" t="n"/>
     </row>
     <row r="31" ht="56" customHeight="1" s="1">
-      <c r="A31" s="49" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>五、黄金ETF（518880）建仓（底仓+定投+大跌加码）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="1">
-      <c r="A32" s="47" t="inlineStr">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="C32" s="49" t="inlineStr">
+      <c r="C32" s="61" t="inlineStr">
         <is>
           <t>单次投入</t>
         </is>
       </c>
-      <c r="D32" s="49" t="inlineStr">
+      <c r="D32" s="61" t="inlineStr">
         <is>
           <t>累计投入</t>
         </is>
       </c>
-      <c r="E32" s="49" t="inlineStr">
+      <c r="E32" s="61" t="inlineStr">
         <is>
           <t>仓位进度</t>
         </is>
       </c>
     </row>
     <row r="33" ht="14.5" customHeight="1" s="1">
-      <c r="A33" s="50" t="inlineStr">
+      <c r="A33" s="62" t="inlineStr">
         <is>
           <t>底仓先行</t>
         </is>
       </c>
-      <c r="B33" s="50" t="inlineStr">
+      <c r="B33" s="62" t="inlineStr">
         <is>
           <t>立即执行</t>
         </is>
       </c>
-      <c r="C33" s="50" t="inlineStr">
+      <c r="C33" s="62" t="inlineStr">
         <is>
           <t>25万</t>
         </is>
       </c>
-      <c r="D33" s="50" t="inlineStr">
+      <c r="D33" s="62" t="inlineStr">
         <is>
           <t>25万</t>
         </is>
       </c>
-      <c r="E33" s="50" t="inlineStr">
+      <c r="E33" s="62" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="14.5" customHeight="1" s="1">
-      <c r="A34" s="52" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>定投阶段</t>
         </is>
       </c>
-      <c r="B34" s="52" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>每月固定（第2-12月）</t>
         </is>
       </c>
-      <c r="C34" s="52" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>4.5万/月</t>
         </is>
       </c>
-      <c r="D34" s="52" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>25-70万</t>
         </is>
       </c>
-      <c r="E34" s="52" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>33%-93%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.5" customHeight="1" s="1">
-      <c r="A35" s="52" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>大跌加码</t>
         </is>
       </c>
-      <c r="B35" s="52" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>单月跌幅超5%</t>
         </is>
       </c>
-      <c r="C35" s="52" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>5万/次</t>
         </is>
       </c>
-      <c r="D35" s="52" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>累计不超过75万</t>
         </is>
       </c>
-      <c r="E35" s="52" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>灵活补充</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.5" customHeight="1" s="1">
-      <c r="A36" s="52" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>收官</t>
         </is>
       </c>
-      <c r="B36" s="52" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>12个月完成或累计达75万</t>
         </is>
       </c>
-      <c r="C36" s="52" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>补齐剩余</t>
         </is>
       </c>
-      <c r="D36" s="52" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>75万</t>
         </is>
       </c>
-      <c r="E36" s="52" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.5" customHeight="1" s="1">
-      <c r="A37" s="52" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>配套规则：时间强制轨道(3月未加码第4月强制4.5万) | 右侧修正(突破前高连5日站稳追入) | 硬止损(-20%且2周暂停)</t>
         </is>
       </c>
-      <c r="B37" s="53" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
-      <c r="E37" s="53" t="n"/>
+      <c r="B37" s="64" t="n"/>
+      <c r="C37" s="64" t="n"/>
+      <c r="D37" s="64" t="n"/>
+      <c r="E37" s="64" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="0" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="57" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>六、盈利提取规则</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1" s="1">
-      <c r="A40" s="54" t="inlineStr">
+      <c r="A40" s="65" t="inlineStr">
         <is>
           <t>年收益&gt;15%时提取50%至独立现金账户，作为胜利果实锁定，不计入再平衡</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="1">
-      <c r="A42" s="47" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr">
         <is>
           <t>七、流动性三原则</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.5" customHeight="1" s="1">
-      <c r="A43" s="50" t="inlineStr">
+      <c r="A43" s="62" t="inlineStr">
         <is>
           <t>511360短融ETF（目标6.25%=25万）：T+0现金管理工具，类现金合计&gt;=25万</t>
         </is>
       </c>
-      <c r="B43" s="51" t="n"/>
-      <c r="C43" s="51" t="n"/>
-      <c r="D43" s="51" t="n"/>
-      <c r="E43" s="51" t="n"/>
+      <c r="B43" s="63" t="n"/>
+      <c r="C43" s="63" t="n"/>
+      <c r="D43" s="63" t="n"/>
+      <c r="E43" s="63" t="n"/>
     </row>
     <row r="44" ht="14.5" customHeight="1" s="1">
-      <c r="A44" s="53" t="n"/>
-      <c r="B44" s="53" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
-      <c r="E44" s="53" t="n"/>
+      <c r="A44" s="64" t="n"/>
+      <c r="B44" s="64" t="n"/>
+      <c r="C44" s="64" t="n"/>
+      <c r="D44" s="64" t="n"/>
+      <c r="E44" s="64" t="n"/>
     </row>
     <row r="45" ht="14.5" customHeight="1" s="1">
-      <c r="A45" s="52" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>━━━ V3回测验证（2021-2025）━━━</t>
         </is>
       </c>
-      <c r="B45" s="53" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
-      <c r="E45" s="53" t="n"/>
+      <c r="B45" s="64" t="n"/>
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="64" t="n"/>
+      <c r="E45" s="64" t="n"/>
     </row>
     <row r="46" ht="14.5" customHeight="1" s="1">
-      <c r="A46" s="52" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>规则组合：止盈+20%卖半 + 止损-15%清仓观察20日 + 年度±20%再平衡</t>
         </is>
       </c>
-      <c r="B46" s="53" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
-      <c r="E46" s="53" t="n"/>
+      <c r="B46" s="64" t="n"/>
+      <c r="C46" s="64" t="n"/>
+      <c r="D46" s="64" t="n"/>
+      <c r="E46" s="64" t="n"/>
     </row>
     <row r="47" ht="14.5" customHeight="1" s="1">
-      <c r="A47" s="52" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>CAGR: +6.66% | 累计收益: +151.8万(+37.94%) | 5年总交易: 71笔</t>
         </is>
       </c>
-      <c r="B47" s="53" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
-      <c r="E47" s="53" t="n"/>
+      <c r="B47" s="64" t="n"/>
+      <c r="C47" s="64" t="n"/>
+      <c r="D47" s="64" t="n"/>
+      <c r="E47" s="64" t="n"/>
     </row>
     <row r="48" ht="84" customHeight="1" s="1">
-      <c r="A48" s="49" t="inlineStr">
+      <c r="A48" s="61" t="inlineStr">
         <is>
           <t>各年收益：2021(+0.82%) 2022(-0.07%) 2023(+5.11%) 2024(+16.11%) 2025(+27.17%)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1" s="1">
-      <c r="A49" s="57" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>对比：同期买入持有CAGR +5.81% | 黄金不适用止盈止损，长期持有</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="1">
-      <c r="A51" s="58" t="n"/>
+      <c r="A51" s="69" t="n"/>
     </row>
     <row r="52" ht="14.5" customHeight="1" s="1">
-      <c r="A52" s="59" t="n"/>
+      <c r="A52" s="70" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="1">
-      <c r="A54" s="58" t="n"/>
+      <c r="A54" s="69" t="n"/>
     </row>
     <row r="55" ht="14.5" customHeight="1" s="1">
-      <c r="A55" s="59" t="n"/>
+      <c r="A55" s="70" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2366,199 +2361,195 @@
     <col width="12" customWidth="1" style="1" min="5" max="5"/>
     <col width="11.7818181818182" customWidth="1" style="1" min="6" max="6"/>
     <col width="9.66363636363636" customWidth="1" style="1" min="7" max="7"/>
-    <col width="10.6363636363636" customWidth="1" style="60" min="8" max="8"/>
-    <col width="10.6363636363636" customWidth="1" style="61" min="9" max="9"/>
-    <col width="16.4454545454545" customWidth="1" style="62" min="10" max="10"/>
-    <col width="14.2181818181818" customWidth="1" style="63" min="11" max="11"/>
+    <col width="10.6363636363636" customWidth="1" style="71" min="8" max="8"/>
+    <col width="10.6363636363636" customWidth="1" style="72" min="9" max="9"/>
+    <col width="16.4454545454545" customWidth="1" style="73" min="10" max="10"/>
+    <col width="14.2181818181818" customWidth="1" style="74" min="11" max="11"/>
     <col width="15.1818181818182" customWidth="1" style="1" min="12" max="12"/>
-    <col width="10.6363636363636" customWidth="1" style="63" min="13" max="13"/>
-    <col width="118.636363636364" customWidth="1" style="64" min="14" max="14"/>
+    <col width="10.6363636363636" customWidth="1" style="74" min="13" max="13"/>
+    <col width="118.636363636364" customWidth="1" style="75" min="14" max="14"/>
     <col width="39.9090909090909" customWidth="1" style="1" min="15" max="15"/>
     <col width="9.54545454545454" customWidth="1" style="1" min="16" max="16"/>
     <col width="12.8181818181818" customWidth="1" style="1" min="17" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="115.2" customHeight="1" s="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>更新日期: 2026-07-01 (数据日期: 2026-07-01)</t>
-        </is>
-      </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>更新日期: 2026-07-02 (数据日期: 2026-07-02)</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>总金额</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>目标金额</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>目标权重</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>当前权重</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>偏离</t>
         </is>
       </c>
-      <c r="H1" s="65" t="inlineStr">
+      <c r="H1" s="76" t="inlineStr">
         <is>
           <t>成本价</t>
         </is>
       </c>
-      <c r="I1" s="66" t="inlineStr">
+      <c r="I1" s="77" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="J1" s="67" t="inlineStr">
+      <c r="J1" s="78" t="inlineStr">
         <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="29" t="inlineStr">
         <is>
           <t>今日收盘价</t>
         </is>
       </c>
-      <c r="L1" s="67" t="inlineStr">
+      <c r="L1" s="78" t="inlineStr">
         <is>
           <t>浮盈/亏</t>
         </is>
       </c>
-      <c r="M1" s="68" t="inlineStr">
+      <c r="M1" s="79" t="inlineStr">
         <is>
           <t>浮盈/亏率</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>建仓计划</t>
         </is>
       </c>
     </row>
-    <row r="2" customFormat="1" s="10">
-      <c r="A2" s="22" t="n">
+    <row r="2" customFormat="1" s="22">
+      <c r="A2" s="34" t="n">
         <v>510300</v>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C2" s="69" t="n">
+      <c r="C2" s="80" t="n">
         <v>4000000</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="81">
         <f>E2*C2</f>
         <v/>
       </c>
-      <c r="E2" s="26" t="n">
+      <c r="E2" s="38" t="n">
         <v>0.1875</v>
       </c>
-      <c r="F2" s="71" t="n">
-        <v>0.2274</v>
-      </c>
-      <c r="G2" s="71" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="H2" s="72" t="n">
+      <c r="F2" s="82" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="G2" s="82" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="H2" s="83" t="n">
         <v>4.885</v>
       </c>
-      <c r="I2" s="73" t="n">
+      <c r="I2" s="84" t="n">
         <v>153800</v>
       </c>
-      <c r="J2" s="74">
+      <c r="J2" s="85">
         <f>H2*I2</f>
         <v/>
       </c>
-      <c r="K2" s="75" t="n">
-        <v>5.019</v>
-      </c>
-      <c r="L2" s="76" t="n">
-        <v>20609.2</v>
-      </c>
-      <c r="M2" s="77" t="n">
-        <v>0.0274</v>
-      </c>
-      <c r="N2" s="23" t="n"/>
-      <c r="O2" s="78" t="n"/>
-      <c r="P2" s="35" t="n"/>
-      <c r="Q2" s="35" t="n"/>
-      <c r="R2" s="10" t="n">
+      <c r="K2" s="86" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="L2" s="87" t="n">
+        <v>-5383</v>
+      </c>
+      <c r="M2" s="88" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="N2" s="35" t="n"/>
+      <c r="O2" s="89" t="n"/>
+      <c r="P2" s="47" t="n"/>
+      <c r="Q2" s="47" t="n"/>
+      <c r="R2" s="22" t="n">
         <v>42600</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="n">
+      <c r="A3" s="48" t="n">
         <v>588050</v>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="48" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C3" s="79" t="n">
+      <c r="C3" s="90" t="n">
         <v>4000000</v>
       </c>
-      <c r="D3" s="80">
+      <c r="D3" s="91">
         <f>E3*C3</f>
         <v/>
       </c>
-      <c r="E3" s="39" t="n">
+      <c r="E3" s="51" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F3" s="81" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="G3" s="81" t="n">
-        <v>-0.0223</v>
-      </c>
-      <c r="H3" s="82" t="n">
+      <c r="F3" s="92" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="G3" s="92" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="H3" s="93" t="n">
         <v>1.838</v>
       </c>
-      <c r="I3" s="83" t="n">
-        <v>60000</v>
-      </c>
-      <c r="J3" s="84">
+      <c r="I3" s="94" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J3" s="95">
         <f>H3*I3</f>
         <v/>
       </c>
-      <c r="K3" s="85" t="n">
-        <v>2.277</v>
-      </c>
-      <c r="L3" s="86" t="n">
-        <v>26340</v>
-      </c>
-      <c r="M3" s="68" t="n">
-        <v>0.2388</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>🟢V3止盈：浮盈23.9% &gt;= +20%，卖半仓，资金转入511360短融ETF</t>
-        </is>
-      </c>
-      <c r="O3" s="78" t="inlineStr">
-        <is>
-          <t>42,600份(部分建仓)</t>
+      <c r="K3" s="96" t="n">
+        <v>2.044</v>
+      </c>
+      <c r="L3" s="97" t="n">
+        <v>6180</v>
+      </c>
+      <c r="M3" s="79" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="N3" s="15" t="n"/>
+      <c r="O3" s="89" t="inlineStr">
+        <is>
+          <t>已完成减半仓</t>
         </is>
       </c>
       <c r="R3" s="0" t="n">
@@ -2566,386 +2557,386 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n">
+      <c r="A4" s="34" t="n">
         <v>159915</v>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>易方达创业板ETF</t>
         </is>
       </c>
-      <c r="C4" s="69" t="n">
+      <c r="C4" s="80" t="n">
         <v>4000000</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="81">
         <f>E4*C4</f>
         <v/>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="38" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F4" s="71" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="G4" s="71" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="H4" s="75" t="n">
+      <c r="F4" s="82" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="G4" s="82" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="H4" s="86" t="n">
         <v>3.968</v>
       </c>
-      <c r="I4" s="73" t="n">
+      <c r="I4" s="84" t="n">
         <v>63000</v>
       </c>
-      <c r="J4" s="74">
+      <c r="J4" s="85">
         <f>H4*I4</f>
         <v/>
       </c>
-      <c r="K4" s="85" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="L4" s="76" t="n">
-        <v>24948</v>
-      </c>
-      <c r="M4" s="77" t="n">
-        <v>0.0998</v>
-      </c>
-      <c r="N4" s="23" t="n"/>
-      <c r="O4" s="78" t="inlineStr">
+      <c r="K4" s="96" t="n">
+        <v>4.036</v>
+      </c>
+      <c r="L4" s="87" t="n">
+        <v>4284</v>
+      </c>
+      <c r="M4" s="88" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="N4" s="35" t="n"/>
+      <c r="O4" s="89" t="inlineStr">
         <is>
           <t>建仓完成</t>
         </is>
       </c>
     </row>
-    <row r="5" customFormat="1" s="10">
-      <c r="A5" s="22" t="n">
+    <row r="5" customFormat="1" s="22">
+      <c r="A5" s="34" t="n">
         <v>512890</v>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>华泰柏瑞红利低波ETF</t>
         </is>
       </c>
-      <c r="C5" s="69" t="n">
+      <c r="C5" s="80" t="n">
         <v>4000000</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="81">
         <f>E5*C5</f>
         <v/>
       </c>
-      <c r="E5" s="26" t="n">
+      <c r="E5" s="38" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F5" s="71" t="n">
-        <v>0.06850000000000001</v>
-      </c>
-      <c r="G5" s="71" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="H5" s="75" t="n">
+      <c r="F5" s="82" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G5" s="82" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="H5" s="86" t="n">
         <v>1.15</v>
       </c>
-      <c r="I5" s="73" t="n">
+      <c r="I5" s="84" t="n">
         <v>218000</v>
       </c>
-      <c r="J5" s="74">
+      <c r="J5" s="85">
         <f>H5*I5</f>
         <v/>
       </c>
-      <c r="K5" s="85" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="L5" s="76" t="n">
-        <v>-18094</v>
-      </c>
-      <c r="M5" s="77" t="n">
-        <v>-0.0722</v>
-      </c>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="78" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="10">
-      <c r="A6" s="36" t="n">
+      <c r="K5" s="96" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="L5" s="87" t="n">
+        <v>-13734</v>
+      </c>
+      <c r="M5" s="88" t="n">
+        <v>-0.0548</v>
+      </c>
+      <c r="N5" s="35" t="n"/>
+      <c r="O5" s="89" t="n"/>
+    </row>
+    <row r="6" customFormat="1" s="22">
+      <c r="A6" s="48" t="n">
         <v>511380</v>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C6" s="79" t="n">
+      <c r="C6" s="90" t="n">
         <v>4000000</v>
       </c>
-      <c r="D6" s="80">
+      <c r="D6" s="91">
         <f>E6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="51" t="n">
         <v>0.125</v>
       </c>
-      <c r="F6" s="81" t="n">
-        <v>0.0596</v>
-      </c>
-      <c r="G6" s="81" t="n">
-        <v>-0.0654</v>
-      </c>
-      <c r="H6" s="82" t="n">
+      <c r="F6" s="92" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="G6" s="92" t="n">
+        <v>-0.0645</v>
+      </c>
+      <c r="H6" s="93" t="n">
         <v>13.8644</v>
       </c>
-      <c r="I6" s="83" t="n">
+      <c r="I6" s="94" t="n">
         <v>14500</v>
       </c>
-      <c r="J6" s="84">
+      <c r="J6" s="95">
         <f>H6*I6</f>
         <v/>
       </c>
-      <c r="K6" s="82" t="n">
-        <v>13.954</v>
-      </c>
-      <c r="L6" s="86" t="n">
-        <v>1299.2</v>
-      </c>
-      <c r="M6" s="68" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="78">
+      <c r="K6" s="93" t="n">
+        <v>13.942</v>
+      </c>
+      <c r="L6" s="97" t="n">
+        <v>1125.2</v>
+      </c>
+      <c r="M6" s="79" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="89">
         <f>D6-J6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="34" t="n">
         <v>511260</v>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>国泰上证10年期国债ETF</t>
         </is>
       </c>
-      <c r="C7" s="69" t="n">
+      <c r="C7" s="80" t="n">
         <v>4000000</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="81">
         <f>E7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="38" t="n">
         <v>0.125</v>
       </c>
-      <c r="F7" s="71" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="G7" s="71" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="H7" s="75" t="n">
+      <c r="F7" s="82" t="n">
+        <v>0.1493</v>
+      </c>
+      <c r="G7" s="82" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="H7" s="86" t="n">
         <v>135.645</v>
       </c>
-      <c r="I7" s="73" t="n">
+      <c r="I7" s="84" t="n">
         <v>3700</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="85">
         <f>H7*I7</f>
         <v/>
       </c>
-      <c r="K7" s="85" t="n">
-        <v>134.854</v>
-      </c>
-      <c r="L7" s="76" t="n">
-        <v>-2926.7</v>
-      </c>
-      <c r="M7" s="77" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="N7" s="23" t="n"/>
-      <c r="O7" s="78" t="n"/>
-    </row>
-    <row r="8" customFormat="1" s="10">
-      <c r="A8" s="22" t="n">
+      <c r="K7" s="96" t="n">
+        <v>134.766</v>
+      </c>
+      <c r="L7" s="87" t="n">
+        <v>-3252.3</v>
+      </c>
+      <c r="M7" s="88" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="N7" s="35" t="n"/>
+      <c r="O7" s="89" t="n"/>
+    </row>
+    <row r="8" customFormat="1" s="22">
+      <c r="A8" s="34" t="n">
         <v>511010</v>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>国泰上证5年期国债ETF</t>
         </is>
       </c>
-      <c r="C8" s="69" t="n">
+      <c r="C8" s="80" t="n">
         <v>4000000</v>
       </c>
-      <c r="D8" s="70">
+      <c r="D8" s="81">
         <f>E8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="38" t="n">
         <v>0.125</v>
       </c>
-      <c r="F8" s="71" t="n">
-        <v>0.1452</v>
-      </c>
-      <c r="G8" s="71" t="n">
-        <v>0.0202</v>
-      </c>
-      <c r="H8" s="75" t="n">
+      <c r="F8" s="82" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="G8" s="82" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="H8" s="86" t="n">
         <v>141.2121</v>
       </c>
-      <c r="I8" s="73" t="n">
+      <c r="I8" s="84" t="n">
         <v>3500</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="85">
         <f>H8*I8</f>
         <v/>
       </c>
-      <c r="K8" s="85" t="n">
-        <v>140.792</v>
-      </c>
-      <c r="L8" s="76" t="n">
-        <v>-1470.35</v>
-      </c>
-      <c r="M8" s="77" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="N8" s="23" t="n"/>
-      <c r="O8" s="78" t="n"/>
-    </row>
-    <row r="9" customFormat="1" s="10">
-      <c r="A9" s="22" t="n">
+      <c r="K8" s="96" t="n">
+        <v>140.695</v>
+      </c>
+      <c r="L8" s="87" t="n">
+        <v>-1809.85</v>
+      </c>
+      <c r="M8" s="88" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="N8" s="35" t="n"/>
+      <c r="O8" s="89" t="n"/>
+    </row>
+    <row r="9" customFormat="1" s="22">
+      <c r="A9" s="34" t="n">
         <v>511360</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>海富通中证短融ETF</t>
         </is>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="80" t="n">
         <v>4000000</v>
       </c>
-      <c r="D9" s="70">
+      <c r="D9" s="81">
         <f>E9*C9</f>
         <v/>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="38" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F9" s="71" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="G9" s="71" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H9" s="75" t="n">
-        <v>113.462</v>
-      </c>
-      <c r="I9" s="73" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J9" s="74">
+      <c r="F9" s="82" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="G9" s="82" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="H9" s="86" t="n">
+        <v>113.4903</v>
+      </c>
+      <c r="I9" s="84" t="n">
+        <v>2700</v>
+      </c>
+      <c r="J9" s="85">
         <f>H9*I9</f>
         <v/>
       </c>
-      <c r="K9" s="85" t="n">
-        <v>113.61</v>
-      </c>
-      <c r="L9" s="76" t="n">
-        <v>325.6</v>
-      </c>
-      <c r="M9" s="77" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="78" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="10">
-      <c r="A10" s="36" t="n">
+      <c r="K9" s="96" t="n">
+        <v>113.626</v>
+      </c>
+      <c r="L9" s="87" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="M9" s="88" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N9" s="35" t="n"/>
+      <c r="O9" s="89" t="n"/>
+    </row>
+    <row r="10" customFormat="1" s="22">
+      <c r="A10" s="48" t="n">
         <v>518880</v>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="48" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="C10" s="79" t="n">
+      <c r="C10" s="90" t="n">
         <v>4000000</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="91">
         <f>E10*C10</f>
         <v/>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="51" t="n">
         <v>0.1875</v>
       </c>
-      <c r="F10" s="81" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="G10" s="81" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H10" s="87" t="n">
+      <c r="F10" s="92" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="G10" s="92" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="H10" s="98" t="n">
         <v>9.1196</v>
       </c>
-      <c r="I10" s="83" t="n">
+      <c r="I10" s="94" t="n">
         <v>63800</v>
       </c>
-      <c r="J10" s="84">
+      <c r="J10" s="95">
         <f>H10*I10</f>
         <v/>
       </c>
-      <c r="K10" s="85" t="n">
-        <v>8.378</v>
-      </c>
-      <c r="L10" s="86" t="n">
-        <v>-47314.08</v>
-      </c>
-      <c r="M10" s="68" t="n">
-        <v>-0.0813</v>
-      </c>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="78">
+      <c r="K10" s="96" t="n">
+        <v>8.475</v>
+      </c>
+      <c r="L10" s="97" t="n">
+        <v>-41125.48</v>
+      </c>
+      <c r="M10" s="79" t="n">
+        <v>-0.0707</v>
+      </c>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="89">
         <f>D10-J10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="84">
+      <c r="A11" s="15" t="inlineStr"/>
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr"/>
+      <c r="D11" s="95">
         <f>SUM(D2:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="39" t="n"/>
-      <c r="F11" s="39" t="n"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="82" t="inlineStr"/>
-      <c r="I11" s="83" t="inlineStr"/>
-      <c r="J11" s="84">
+      <c r="E11" s="51" t="n"/>
+      <c r="F11" s="51" t="n"/>
+      <c r="G11" s="15" t="inlineStr"/>
+      <c r="H11" s="93" t="inlineStr"/>
+      <c r="I11" s="94" t="inlineStr"/>
+      <c r="J11" s="95">
         <f>SUM(J2:J10)</f>
         <v/>
       </c>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="84">
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="95">
         <f>SUM(L2:L10)</f>
         <v/>
       </c>
-      <c r="M11" s="68">
+      <c r="M11" s="79">
         <f>L11/J11</f>
         <v/>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="15" t="inlineStr">
         <is>
           <t>👀 偏离关注：相对偏离-16.7%（低配，接近±20%阀值）</t>
         </is>
       </c>
-      <c r="O11" s="84" t="inlineStr">
+      <c r="O11" s="95" t="inlineStr">
         <is>
           <t>底仓25万+定投4.5万/月+大跌加码5万</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="J14" s="88" t="n"/>
+      <c r="J14" s="99" t="n"/>
     </row>
     <row r="18">
-      <c r="J18" s="88" t="n"/>
+      <c r="J18" s="99" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2958,10 +2949,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="20.8181818181818" customWidth="1" style="89" min="1" max="1"/>
+    <col width="20.8181818181818" customWidth="1" style="100" min="1" max="1"/>
     <col width="7.54545454545455" customWidth="1" style="1" min="2" max="2"/>
     <col width="12.9090909090909" customWidth="1" style="1" min="3" max="3"/>
     <col width="10.6363636363636" customWidth="1" style="1" min="4" max="4"/>
@@ -2970,674 +2961,730 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="101" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="D2" s="91" t="n">
+      <c r="D2" s="102" t="n">
         <v>113.462</v>
       </c>
-      <c r="E2" s="83" t="n">
+      <c r="E2" s="94" t="n">
         <v>2200</v>
       </c>
-      <c r="F2" s="84" t="n">
+      <c r="F2" s="95" t="n">
         <v>249616.4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="90" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D3" s="91" t="n">
+      <c r="D3" s="102" t="n">
         <v>9.497999999999999</v>
       </c>
-      <c r="E3" s="83" t="n">
+      <c r="E3" s="94" t="n">
         <v>15800</v>
       </c>
-      <c r="F3" s="84" t="n">
+      <c r="F3" s="95" t="n">
         <v>150068.4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="90" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>五年国债ETF</t>
         </is>
       </c>
-      <c r="D4" s="91" t="n">
+      <c r="D4" s="102" t="n">
         <v>141.253</v>
       </c>
-      <c r="E4" s="83" t="n">
+      <c r="E4" s="94" t="n">
         <v>800</v>
       </c>
-      <c r="F4" s="84" t="n">
+      <c r="F4" s="95" t="n">
         <v>113002.4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="90" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>十年国债ETF</t>
         </is>
       </c>
-      <c r="D5" s="91" t="n">
+      <c r="D5" s="102" t="n">
         <v>135.645</v>
       </c>
-      <c r="E5" s="83" t="n">
+      <c r="E5" s="94" t="n">
         <v>3700</v>
       </c>
-      <c r="F5" s="84" t="n">
+      <c r="F5" s="95" t="n">
         <v>501886.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="D6" s="91" t="n">
+      <c r="D6" s="102" t="n">
         <v>4.942</v>
       </c>
-      <c r="E6" s="83" t="n">
+      <c r="E6" s="94" t="n">
         <v>70000</v>
       </c>
-      <c r="F6" s="84" t="n">
+      <c r="F6" s="95" t="n">
         <v>345940</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="90" t="inlineStr">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="D7" s="91" t="n">
+      <c r="D7" s="102" t="n">
         <v>3.968</v>
       </c>
-      <c r="E7" s="83" t="n">
+      <c r="E7" s="94" t="n">
         <v>63000</v>
       </c>
-      <c r="F7" s="84" t="n">
+      <c r="F7" s="95" t="n">
         <v>249984</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="90" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="D8" s="91" t="n">
+      <c r="D8" s="102" t="n">
         <v>8.696</v>
       </c>
-      <c r="E8" s="83" t="n">
+      <c r="E8" s="94" t="n">
         <v>4000</v>
       </c>
-      <c r="F8" s="84" t="n">
+      <c r="F8" s="95" t="n">
         <v>34784</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="90" t="inlineStr">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>510500</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="D9" s="91" t="n">
+      <c r="D9" s="102" t="n">
         <v>8.696</v>
       </c>
-      <c r="E9" s="83" t="n">
+      <c r="E9" s="94" t="n">
         <v>16000</v>
       </c>
-      <c r="F9" s="84" t="n">
+      <c r="F9" s="95" t="n">
         <v>139136</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="D10" s="91" t="n">
+      <c r="D10" s="102" t="n">
         <v>4.865</v>
       </c>
-      <c r="E10" s="83" t="n">
+      <c r="E10" s="94" t="n">
         <v>40000</v>
       </c>
-      <c r="F10" s="84" t="n">
+      <c r="F10" s="95" t="n">
         <v>194600</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="90" t="inlineStr">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="D11" s="91" t="n">
+      <c r="D11" s="102" t="n">
         <v>1.838</v>
       </c>
-      <c r="E11" s="83" t="n">
+      <c r="E11" s="94" t="n">
         <v>60000</v>
       </c>
-      <c r="F11" s="84" t="n">
+      <c r="F11" s="95" t="n">
         <v>110280</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="90" t="inlineStr">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>五年国债ETF</t>
         </is>
       </c>
-      <c r="D12" s="91" t="n">
+      <c r="D12" s="102" t="n">
         <v>141.2</v>
       </c>
-      <c r="E12" s="83" t="n">
+      <c r="E12" s="94" t="n">
         <v>2700</v>
       </c>
-      <c r="F12" s="84" t="n">
+      <c r="F12" s="95" t="n">
         <v>381240</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="16" t="n">
         <v>512890</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>华泰柏瑞红利低波ETF</t>
         </is>
       </c>
-      <c r="D13" s="91" t="n">
+      <c r="D13" s="102" t="n">
         <v>1.15</v>
       </c>
-      <c r="E13" s="83" t="n">
+      <c r="E13" s="94" t="n">
         <v>218000</v>
       </c>
-      <c r="F13" s="84" t="n">
+      <c r="F13" s="95" t="n">
         <v>250700</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="92" t="inlineStr">
+      <c r="A14" s="103" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="16" t="n">
         <v>518880</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D14" s="91" t="n">
+      <c r="D14" s="102" t="n">
         <v>9.455</v>
       </c>
-      <c r="E14" s="83" t="n">
+      <c r="E14" s="94" t="n">
         <v>8000</v>
       </c>
-      <c r="F14" s="84" t="n">
+      <c r="F14" s="95" t="n">
         <v>75640</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="90" t="inlineStr">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="16" t="n">
         <v>518880</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D15" s="91" t="n">
+      <c r="D15" s="102" t="n">
         <v>9.385</v>
       </c>
-      <c r="E15" s="83" t="n">
+      <c r="E15" s="94" t="n">
         <v>8000</v>
       </c>
-      <c r="F15" s="84" t="n">
+      <c r="F15" s="95" t="n">
         <v>75080</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="90" t="inlineStr">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="16" t="n">
         <v>518880</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D16" s="91" t="n">
+      <c r="D16" s="102" t="n">
         <v>9.15</v>
       </c>
-      <c r="E16" s="83" t="n">
+      <c r="E16" s="94" t="n">
         <v>8000</v>
       </c>
-      <c r="F16" s="84" t="n">
+      <c r="F16" s="95" t="n">
         <v>73200</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="90" t="inlineStr">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="16" t="n">
         <v>511990</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="D17" s="91" t="n">
+      <c r="D17" s="102" t="n">
         <v>99.997</v>
       </c>
-      <c r="E17" s="83" t="n">
+      <c r="E17" s="94" t="n">
         <v>2500</v>
       </c>
-      <c r="F17" s="84" t="n">
+      <c r="F17" s="95" t="n">
         <v>249992.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="90" t="inlineStr">
+      <c r="A18" s="101" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="D18" s="91" t="n">
+      <c r="D18" s="102" t="n">
         <v>13.95</v>
       </c>
-      <c r="E18" s="83" t="n">
+      <c r="E18" s="94" t="n">
         <v>7200</v>
       </c>
-      <c r="F18" s="84" t="n">
+      <c r="F18" s="95" t="n">
         <v>100440</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="90" t="inlineStr">
+      <c r="A19" s="101" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>511990</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>华宝添益ETF</t>
         </is>
       </c>
-      <c r="D19" s="91" t="n">
+      <c r="D19" s="102" t="n">
         <v>100.005</v>
       </c>
-      <c r="E19" s="83" t="n">
+      <c r="E19" s="94" t="n">
         <v>-2500</v>
       </c>
-      <c r="F19" s="84" t="n">
+      <c r="F19" s="95" t="n">
         <v>-250012.5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="90" t="inlineStr">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="16" t="n">
         <v>510300</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="D20" s="91" t="n">
+      <c r="D20" s="102" t="n">
         <v>4.85</v>
       </c>
-      <c r="E20" s="83" t="n">
+      <c r="E20" s="94" t="n">
         <v>20000</v>
       </c>
-      <c r="F20" s="84" t="n">
+      <c r="F20" s="95" t="n">
         <v>97000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="90" t="inlineStr">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D21" s="91" t="n">
+      <c r="D21" s="102" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="83" t="n">
+      <c r="E21" s="94" t="n">
         <v>8000</v>
       </c>
-      <c r="F21" s="84" t="n">
+      <c r="F21" s="95" t="n">
         <v>72000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="90" t="inlineStr">
+      <c r="A22" s="101" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="D22" s="91" t="n">
+      <c r="D22" s="102" t="n">
         <v>4.78</v>
       </c>
-      <c r="E22" s="83" t="n">
+      <c r="E22" s="94" t="n">
         <v>23800</v>
       </c>
-      <c r="F22" s="84" t="n">
+      <c r="F22" s="95" t="n">
         <v>113764</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="90" t="inlineStr">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="D23" s="91" t="n">
+      <c r="D23" s="102" t="n">
         <v>13.78</v>
       </c>
-      <c r="E23" s="83" t="n">
+      <c r="E23" s="94" t="n">
         <v>7300</v>
       </c>
-      <c r="F23" s="84" t="n">
+      <c r="F23" s="95" t="n">
         <v>100594</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="90" t="inlineStr">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D24" s="91" t="n">
+      <c r="D24" s="102" t="n">
         <v>8.65</v>
       </c>
-      <c r="E24" s="83" t="n">
+      <c r="E24" s="94" t="n">
         <v>8000</v>
       </c>
-      <c r="F24" s="84" t="n">
+      <c r="F24" s="95" t="n">
         <v>69200</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="90" t="inlineStr">
+      <c r="A25" s="101" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="16" t="n">
         <v>510500</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>中证500ETF</t>
         </is>
       </c>
-      <c r="D25" s="91" t="n">
+      <c r="D25" s="102" t="n">
         <v>8.776999999999999</v>
       </c>
-      <c r="E25" s="83" t="n">
+      <c r="E25" s="94" t="n">
         <v>-20000</v>
       </c>
-      <c r="F25" s="84">
+      <c r="F25" s="95">
         <f>D25*E25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="90" t="inlineStr">
+      <c r="A26" s="101" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="16" t="n">
         <v>518880</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>华安黄金ETF</t>
         </is>
       </c>
-      <c r="D26" s="91" t="n">
+      <c r="D26" s="102" t="n">
         <v>8.33</v>
       </c>
-      <c r="E26" s="83" t="n">
+      <c r="E26" s="94" t="n">
         <v>8000</v>
       </c>
-      <c r="F26" s="84" t="n">
+      <c r="F26" s="95" t="n">
         <v>66640</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="104" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>588050</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>2.121</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>-63630</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>卖出止盈</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="105" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>113.615</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>56807.5</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>止盈转入</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F26"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3648,7 +3695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q258"/>
+  <dimension ref="A1:Q267"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="11.8181818181818" customWidth="1" style="1" min="1" max="1"/>
@@ -17173,7 +17220,7 @@
         <v>135.645</v>
       </c>
       <c r="F246" s="0" t="n">
-        <v>501886.5000000001</v>
+        <v>501886.5</v>
       </c>
       <c r="G246" s="0" t="n">
         <v>134.97</v>
@@ -17368,495 +17415,987 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="0" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="0" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D250" t="n">
+      <c r="D250" s="0" t="n">
         <v>153800</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="0" t="n">
         <v>4.885</v>
       </c>
-      <c r="F250" t="n">
+      <c r="F250" s="0" t="n">
         <v>751313</v>
       </c>
-      <c r="G250" t="n">
-        <v>5.019</v>
-      </c>
-      <c r="H250" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="I250" t="n">
-        <v>771922.2</v>
-      </c>
-      <c r="J250" t="n">
-        <v>20609.2</v>
-      </c>
-      <c r="K250" t="n">
-        <v>0.0274</v>
-      </c>
-      <c r="L250" t="n">
+      <c r="G250" s="0" t="n">
+        <v>4.998</v>
+      </c>
+      <c r="H250" s="0" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="I250" s="0" t="n">
+        <v>768692.4</v>
+      </c>
+      <c r="J250" s="0" t="n">
+        <v>17379.4</v>
+      </c>
+      <c r="K250" s="0" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="L250" s="0" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M250" t="n">
-        <v>0.2274</v>
-      </c>
-      <c r="N250" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="O250" t="inlineStr">
+      <c r="M250" s="0" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="N250" s="0" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="O250" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="0" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C251" s="0" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D251" t="n">
+      <c r="D251" s="0" t="n">
         <v>60000</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" s="0" t="n">
         <v>1.838</v>
       </c>
-      <c r="F251" t="n">
+      <c r="F251" s="0" t="n">
         <v>110280</v>
       </c>
-      <c r="G251" t="n">
-        <v>2.277</v>
-      </c>
-      <c r="H251" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="I251" t="n">
-        <v>136620</v>
-      </c>
-      <c r="J251" t="n">
-        <v>26340</v>
-      </c>
-      <c r="K251" t="n">
-        <v>0.2388</v>
-      </c>
-      <c r="L251" t="n">
+      <c r="G251" s="0" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="H251" s="0" t="n">
+        <v>-0.0255</v>
+      </c>
+      <c r="I251" s="0" t="n">
+        <v>133140</v>
+      </c>
+      <c r="J251" s="0" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K251" s="0" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="L251" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M251" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="N251" t="n">
-        <v>-0.0223</v>
-      </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>🟢V3止盈：浮盈23.9% &gt;= +20%，卖半仓，资金转入511360短融ETF</t>
+      <c r="M251" s="0" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="N251" s="0" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="O251" s="0" t="inlineStr">
+        <is>
+          <t>🟢V3止盈：浮盈20.7% &gt;= +20%，卖半仓，资金转入511360短融ETF</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="0" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C252" s="0" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D252" t="n">
+      <c r="D252" s="0" t="n">
         <v>63000</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="0" t="n">
         <v>3.968</v>
       </c>
-      <c r="F252" t="n">
+      <c r="F252" s="0" t="n">
         <v>249984</v>
       </c>
-      <c r="G252" t="n">
-        <v>4.364</v>
-      </c>
-      <c r="H252" t="n">
-        <v>0.0302</v>
-      </c>
-      <c r="I252" t="n">
-        <v>274932</v>
-      </c>
-      <c r="J252" t="n">
-        <v>24948</v>
-      </c>
-      <c r="K252" t="n">
-        <v>0.0998</v>
-      </c>
-      <c r="L252" t="n">
+      <c r="G252" s="0" t="n">
+        <v>4.274</v>
+      </c>
+      <c r="H252" s="0" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="I252" s="0" t="n">
+        <v>269262</v>
+      </c>
+      <c r="J252" s="0" t="n">
+        <v>19278</v>
+      </c>
+      <c r="K252" s="0" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="L252" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M252" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="N252" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="O252" t="inlineStr">
+      <c r="M252" s="0" t="n">
+        <v>0.07969999999999999</v>
+      </c>
+      <c r="N252" s="0" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="O252" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="0" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="0" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D253" t="n">
+      <c r="D253" s="0" t="n">
         <v>218000</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="0" t="n">
         <v>1.15</v>
       </c>
-      <c r="F253" t="n">
+      <c r="F253" s="0" t="n">
         <v>250700</v>
       </c>
-      <c r="G253" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="H253" t="n">
-        <v>-0.0202</v>
-      </c>
-      <c r="I253" t="n">
-        <v>232606</v>
-      </c>
-      <c r="J253" t="n">
-        <v>-18094</v>
-      </c>
-      <c r="K253" t="n">
-        <v>-0.0722</v>
-      </c>
-      <c r="L253" t="n">
+      <c r="G253" s="0" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="H253" s="0" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="I253" s="0" t="n">
+        <v>235222</v>
+      </c>
+      <c r="J253" s="0" t="n">
+        <v>-15478</v>
+      </c>
+      <c r="K253" s="0" t="n">
+        <v>-0.0617</v>
+      </c>
+      <c r="L253" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M253" t="n">
-        <v>0.06850000000000001</v>
-      </c>
-      <c r="N253" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O253" t="inlineStr">
+      <c r="M253" s="0" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="N253" s="0" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="O253" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="0" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="0" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D254" t="n">
+      <c r="D254" s="0" t="n">
         <v>14500</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="0" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F254" t="n">
+      <c r="F254" s="0" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G254" t="n">
-        <v>13.954</v>
-      </c>
-      <c r="H254" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="I254" t="n">
-        <v>202333</v>
-      </c>
-      <c r="J254" t="n">
-        <v>1299.2</v>
-      </c>
-      <c r="K254" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="L254" t="n">
+      <c r="G254" s="0" t="n">
+        <v>14.004</v>
+      </c>
+      <c r="H254" s="0" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I254" s="0" t="n">
+        <v>203058</v>
+      </c>
+      <c r="J254" s="0" t="n">
+        <v>2024.2</v>
+      </c>
+      <c r="K254" s="0" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="L254" s="0" t="n">
         <v>0.125</v>
       </c>
-      <c r="M254" t="n">
-        <v>0.0596</v>
-      </c>
-      <c r="N254" t="n">
-        <v>-0.0654</v>
-      </c>
-      <c r="O254" t="inlineStr">
+      <c r="M254" s="0" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="N254" s="0" t="n">
+        <v>-0.0649</v>
+      </c>
+      <c r="O254" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="0" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C255" s="0" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D255" t="n">
+      <c r="D255" s="0" t="n">
         <v>3700</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="0" t="n">
         <v>135.645</v>
       </c>
-      <c r="F255" t="n">
+      <c r="F255" s="0" t="n">
         <v>501886.5</v>
       </c>
-      <c r="G255" t="n">
-        <v>134.854</v>
-      </c>
-      <c r="H255" t="n">
-        <v>-0.0009</v>
-      </c>
-      <c r="I255" t="n">
-        <v>498959.8</v>
-      </c>
-      <c r="J255" t="n">
-        <v>-2926.7</v>
-      </c>
-      <c r="K255" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="L255" t="n">
+      <c r="G255" s="0" t="n">
+        <v>134.661</v>
+      </c>
+      <c r="H255" s="0" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="I255" s="0" t="n">
+        <v>498245.7</v>
+      </c>
+      <c r="J255" s="0" t="n">
+        <v>-3640.8</v>
+      </c>
+      <c r="K255" s="0" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="L255" s="0" t="n">
         <v>0.125</v>
       </c>
-      <c r="M255" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="N255" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="O255" t="inlineStr">
+      <c r="M255" s="0" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="N255" s="0" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="O255" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C256" s="0" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D256" t="n">
+      <c r="D256" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="0" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F256" t="n">
+      <c r="F256" s="0" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G256" t="n">
-        <v>140.792</v>
-      </c>
-      <c r="H256" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="I256" t="n">
-        <v>492772</v>
-      </c>
-      <c r="J256" t="n">
-        <v>-1470.35</v>
-      </c>
-      <c r="K256" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="L256" t="n">
+      <c r="G256" s="0" t="n">
+        <v>140.637</v>
+      </c>
+      <c r="H256" s="0" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="I256" s="0" t="n">
+        <v>492229.5</v>
+      </c>
+      <c r="J256" s="0" t="n">
+        <v>-2012.85</v>
+      </c>
+      <c r="K256" s="0" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="L256" s="0" t="n">
         <v>0.125</v>
       </c>
-      <c r="M256" t="n">
-        <v>0.1452</v>
-      </c>
-      <c r="N256" t="n">
-        <v>0.0202</v>
-      </c>
-      <c r="O256" t="inlineStr">
+      <c r="M256" s="0" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="N256" s="0" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="O256" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="0" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="0" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D257" t="n">
+      <c r="D257" s="0" t="n">
         <v>2200</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="0" t="n">
         <v>113.462</v>
       </c>
-      <c r="F257" t="n">
+      <c r="F257" s="0" t="n">
         <v>249616.4</v>
       </c>
-      <c r="G257" t="n">
-        <v>113.61</v>
-      </c>
-      <c r="H257" t="n">
+      <c r="G257" s="0" t="n">
+        <v>113.615</v>
+      </c>
+      <c r="I257" s="0" t="n">
+        <v>249953</v>
+      </c>
+      <c r="J257" s="0" t="n">
+        <v>336.6</v>
+      </c>
+      <c r="K257" s="0" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="L257" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M257" s="0" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="N257" s="0" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="O257" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="D258" s="0" t="n">
+        <v>63800</v>
+      </c>
+      <c r="E258" s="0" t="n">
+        <v>9.1196</v>
+      </c>
+      <c r="F258" s="0" t="n">
+        <v>581830.48</v>
+      </c>
+      <c r="G258" s="0" t="n">
+        <v>8.271000000000001</v>
+      </c>
+      <c r="H258" s="0" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="I258" s="0" t="n">
+        <v>527689.8</v>
+      </c>
+      <c r="J258" s="0" t="n">
+        <v>-54140.68</v>
+      </c>
+      <c r="K258" s="0" t="n">
+        <v>-0.0931</v>
+      </c>
+      <c r="L258" s="0" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M258" s="0" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="N258" s="0" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="O258" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B259" s="0" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="D259" s="0" t="n">
+        <v>153800</v>
+      </c>
+      <c r="E259" s="0" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="F259" s="0" t="n">
+        <v>751313</v>
+      </c>
+      <c r="G259" s="0" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H259" s="0" t="n">
+        <v>-0.0296</v>
+      </c>
+      <c r="I259" s="0" t="n">
+        <v>745930</v>
+      </c>
+      <c r="J259" s="0" t="n">
+        <v>-5383</v>
+      </c>
+      <c r="K259" s="0" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="L259" s="0" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M259" s="0" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="N259" s="0" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="O259" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B260" s="0" t="inlineStr">
+        <is>
+          <t>科创50ETF</t>
+        </is>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t>588050</t>
+        </is>
+      </c>
+      <c r="D260" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E260" s="0" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="F260" s="0" t="n">
+        <v>55140</v>
+      </c>
+      <c r="G260" s="0" t="n">
+        <v>2.044</v>
+      </c>
+      <c r="H260" s="0" t="n">
+        <v>-0.0789</v>
+      </c>
+      <c r="I260" s="0" t="n">
+        <v>61320</v>
+      </c>
+      <c r="J260" s="0" t="n">
+        <v>6180</v>
+      </c>
+      <c r="K260" s="0" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="L260" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M260" s="0" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="N260" s="0" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="O260" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B261" s="0" t="inlineStr">
+        <is>
+          <t>创业板ETF</t>
+        </is>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t>159915</t>
+        </is>
+      </c>
+      <c r="D261" s="0" t="n">
+        <v>63000</v>
+      </c>
+      <c r="E261" s="0" t="n">
+        <v>3.968</v>
+      </c>
+      <c r="F261" s="0" t="n">
+        <v>249984</v>
+      </c>
+      <c r="G261" s="0" t="n">
+        <v>4.036</v>
+      </c>
+      <c r="H261" s="0" t="n">
+        <v>-0.0557</v>
+      </c>
+      <c r="I261" s="0" t="n">
+        <v>254268</v>
+      </c>
+      <c r="J261" s="0" t="n">
+        <v>4284</v>
+      </c>
+      <c r="K261" s="0" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="L261" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M261" s="0" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="N261" s="0" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="O261" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B262" s="0" t="inlineStr">
+        <is>
+          <t>红利低波ETF</t>
+        </is>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="D262" s="0" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E262" s="0" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F262" s="0" t="n">
+        <v>250700</v>
+      </c>
+      <c r="G262" s="0" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="H262" s="0" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="I262" s="0" t="n">
+        <v>236966</v>
+      </c>
+      <c r="J262" s="0" t="n">
+        <v>-13734</v>
+      </c>
+      <c r="K262" s="0" t="n">
+        <v>-0.0548</v>
+      </c>
+      <c r="L262" s="0" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M262" s="0" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="N262" s="0" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="O262" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B263" s="0" t="inlineStr">
+        <is>
+          <t>可转债ETF</t>
+        </is>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t>511380</t>
+        </is>
+      </c>
+      <c r="D263" s="0" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E263" s="0" t="n">
+        <v>13.8644</v>
+      </c>
+      <c r="F263" s="0" t="n">
+        <v>201033.8</v>
+      </c>
+      <c r="G263" s="0" t="n">
+        <v>13.942</v>
+      </c>
+      <c r="H263" s="0" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="I263" s="0" t="n">
+        <v>202159</v>
+      </c>
+      <c r="J263" s="0" t="n">
+        <v>1125.2</v>
+      </c>
+      <c r="K263" s="0" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="L263" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M263" s="0" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="N263" s="0" t="n">
+        <v>-0.0645</v>
+      </c>
+      <c r="O263" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B264" s="0" t="inlineStr">
+        <is>
+          <t>10年国债ETF</t>
+        </is>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t>511260</t>
+        </is>
+      </c>
+      <c r="D264" s="0" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E264" s="0" t="n">
+        <v>135.645</v>
+      </c>
+      <c r="F264" s="0" t="n">
+        <v>501886.5</v>
+      </c>
+      <c r="G264" s="0" t="n">
+        <v>134.766</v>
+      </c>
+      <c r="H264" s="0" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="I264" s="0" t="n">
+        <v>498634.2</v>
+      </c>
+      <c r="J264" s="0" t="n">
+        <v>-3252.3</v>
+      </c>
+      <c r="K264" s="0" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="L264" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M264" s="0" t="n">
+        <v>0.1493</v>
+      </c>
+      <c r="N264" s="0" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="O264" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B265" s="0" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="D265" s="0" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E265" s="0" t="n">
+        <v>141.2121</v>
+      </c>
+      <c r="F265" s="0" t="n">
+        <v>494242.35</v>
+      </c>
+      <c r="G265" s="0" t="n">
+        <v>140.695</v>
+      </c>
+      <c r="H265" s="0" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="I265" s="0" t="n">
+        <v>492432.5</v>
+      </c>
+      <c r="J265" s="0" t="n">
+        <v>-1809.85</v>
+      </c>
+      <c r="K265" s="0" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="L265" s="0" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M265" s="0" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="N265" s="0" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="O265" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B266" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="D266" s="0" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E266" s="0" t="n">
+        <v>113.4903</v>
+      </c>
+      <c r="F266" s="0" t="n">
+        <v>306423.81</v>
+      </c>
+      <c r="G266" s="0" t="n">
+        <v>113.626</v>
+      </c>
+      <c r="H266" s="0" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I257" t="n">
-        <v>249942</v>
-      </c>
-      <c r="J257" t="n">
-        <v>325.6</v>
-      </c>
-      <c r="K257" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="L257" t="n">
+      <c r="I266" s="0" t="n">
+        <v>306790.2</v>
+      </c>
+      <c r="J266" s="0" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="K266" s="0" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="L266" s="0" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M257" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="N257" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
+      <c r="M266" s="0" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="N266" s="0" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="O266" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B267" s="0" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C267" s="0" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D258" t="n">
+      <c r="D267" s="0" t="n">
         <v>63800</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E267" s="0" t="n">
         <v>9.1196</v>
       </c>
-      <c r="F258" t="n">
+      <c r="F267" s="0" t="n">
         <v>581830.48</v>
       </c>
-      <c r="G258" t="n">
-        <v>8.378</v>
-      </c>
-      <c r="H258" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="I258" t="n">
-        <v>534516.4</v>
-      </c>
-      <c r="J258" t="n">
-        <v>-47314.08</v>
-      </c>
-      <c r="K258" t="n">
-        <v>-0.0813</v>
-      </c>
-      <c r="L258" t="n">
+      <c r="G267" s="0" t="n">
+        <v>8.475</v>
+      </c>
+      <c r="H267" s="0" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="I267" s="0" t="n">
+        <v>540705</v>
+      </c>
+      <c r="J267" s="0" t="n">
+        <v>-41125.48</v>
+      </c>
+      <c r="K267" s="0" t="n">
+        <v>-0.0707</v>
+      </c>
+      <c r="L267" s="0" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M258" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="N258" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O258" t="inlineStr">
+      <c r="M267" s="0" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="N267" s="0" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="O267" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -17870,805 +18409,799 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00548235"/>
+    <tabColor rgb="FF548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="22" customWidth="1" style="1" min="1" max="1"/>
-    <col width="22" customWidth="1" style="1" min="2" max="2"/>
-    <col width="22" customWidth="1" style="1" min="3" max="3"/>
-    <col width="22" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22" customWidth="1" style="1" min="1" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1" s="1">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>GA最优方案 — 遗传算法（达尔文优化）结果存档</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>一、四方案参数对比</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="95" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>参数</t>
         </is>
       </c>
-      <c r="B4" s="95" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>当前V3</t>
         </is>
       </c>
-      <c r="C4" s="95" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>GA最优</t>
         </is>
       </c>
-      <c r="D4" s="95" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>网格最佳</t>
         </is>
       </c>
-      <c r="E4" s="95" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>买入持有</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="96" t="inlineStr">
+    <row r="5" ht="14.5" customHeight="1" s="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>止盈触发</t>
         </is>
       </c>
-      <c r="B5" s="96" t="inlineStr">
-        <is>
-          <t>+20%卖半</t>
-        </is>
-      </c>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>&gt;= +31.5%，卖出69%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>+5.1%全卖</t>
         </is>
       </c>
-      <c r="D5" s="96" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>+30%卖半</t>
         </is>
       </c>
-      <c r="E5" s="96" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="96" t="inlineStr">
+    <row r="6" ht="14.5" customHeight="1" s="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>止损触发</t>
         </is>
       </c>
-      <c r="B6" s="96" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= -15.0%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>-19.9%</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>-15%</t>
         </is>
       </c>
-      <c r="C6" s="97" t="inlineStr">
-        <is>
-          <t>-19.9%</t>
-        </is>
-      </c>
-      <c r="D6" s="96" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
-      <c r="E6" s="96" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="96" t="inlineStr">
+    <row r="7" ht="14.5" customHeight="1" s="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>观察期</t>
         </is>
       </c>
-      <c r="B7" s="96" t="inlineStr">
-        <is>
-          <t>20交易日</t>
-        </is>
-      </c>
-      <c r="C7" s="97" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>51 个交易日</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>32交易日</t>
         </is>
       </c>
-      <c r="D7" s="96" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>40交易日</t>
         </is>
       </c>
-      <c r="E7" s="96" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="96" t="inlineStr">
+    <row r="8" ht="14.5" customHeight="1" s="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>再平衡频率</t>
         </is>
       </c>
-      <c r="B8" s="96" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="C8" s="97" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="D8" s="96" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>半年度</t>
         </is>
       </c>
-      <c r="E8" s="96" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="96" t="inlineStr">
+    <row r="9" ht="14.5" customHeight="1" s="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>再平衡阈值</t>
         </is>
       </c>
-      <c r="B9" s="96" t="inlineStr">
-        <is>
-          <t>±20%</t>
-        </is>
-      </c>
-      <c r="C9" s="97" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>+/-39%</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>±28%</t>
         </is>
       </c>
-      <c r="D9" s="96" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>±10%</t>
         </is>
       </c>
-      <c r="E9" s="96" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="94" t="inlineStr">
+    <row r="11" ht="16.5" customHeight="1" s="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>二、回测指标对比（2021-2025，400万）</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="95" t="inlineStr">
+    <row r="12" ht="16.5" customHeight="1" s="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>当前V3</t>
         </is>
       </c>
-      <c r="C12" s="95" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>GA最优</t>
         </is>
       </c>
-      <c r="D12" s="95" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>网格最佳</t>
         </is>
       </c>
-      <c r="E12" s="95" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>买入持有</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="96" t="inlineStr">
+    <row r="13" ht="14.5" customHeight="1" s="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>+5.39%</t>
-        </is>
-      </c>
-      <c r="C13" s="97" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>+12.30%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>+7.00%</t>
         </is>
       </c>
-      <c r="D13" s="96" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>+4.49%</t>
         </is>
       </c>
-      <c r="E13" s="96" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>+5.81%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="96" t="inlineStr">
+    <row r="14" ht="14.5" customHeight="1" s="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>总收益</t>
         </is>
       </c>
-      <c r="B14" s="96" t="inlineStr">
-        <is>
-          <t>+28.72%</t>
-        </is>
-      </c>
-      <c r="C14" s="97" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>+78.33%</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>+38.47%</t>
         </is>
       </c>
-      <c r="D14" s="96" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>+24.50%</t>
         </is>
       </c>
-      <c r="E14" s="96" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>+32.67%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="96" t="inlineStr">
+    <row r="15" ht="14.5" customHeight="1" s="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>最大回撤</t>
         </is>
       </c>
-      <c r="B15" s="96" t="inlineStr">
-        <is>
-          <t>-10.32%</t>
-        </is>
-      </c>
-      <c r="C15" s="97" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>-11.50%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>-8.89%</t>
         </is>
       </c>
-      <c r="D15" s="96" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>-7.96%</t>
         </is>
       </c>
-      <c r="E15" s="96" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>-12.43%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="96" t="inlineStr">
+    <row r="16" ht="14.5" customHeight="1" s="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>夏普比率</t>
         </is>
       </c>
-      <c r="B16" s="96" t="inlineStr">
-        <is>
-          <t>0.705</t>
-        </is>
-      </c>
-      <c r="C16" s="97" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>0.7067</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>1.037</t>
         </is>
       </c>
-      <c r="D16" s="96" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>0.655</t>
         </is>
       </c>
-      <c r="E16" s="96" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>0.802</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="96" t="inlineStr">
+    <row r="17" ht="14.5" customHeight="1" s="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>最终净值</t>
         </is>
       </c>
-      <c r="B17" s="96" t="inlineStr">
-        <is>
-          <t>5,148,903</t>
-        </is>
-      </c>
-      <c r="C17" s="97" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>¥7,133,397</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>5,538,852</t>
         </is>
       </c>
-      <c r="D17" s="96" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>4,980,098</t>
         </is>
       </c>
-      <c r="E17" s="96" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>5,306,710</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="96" t="inlineStr">
+    <row r="18" ht="14.5" customHeight="1" s="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>交易笔数</t>
         </is>
       </c>
-      <c r="B18" s="96" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C18" s="97" t="inlineStr">
+      <c r="B18" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D18" s="96" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E18" s="96" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="94" t="inlineStr">
+    <row r="20" ht="16.5" customHeight="1" s="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>三、逐年组合收益对比</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+    <row r="21" ht="16.5" customHeight="1" s="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>年份</t>
         </is>
       </c>
-      <c r="B21" s="95" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>当前V3</t>
         </is>
       </c>
-      <c r="C21" s="95" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>GA最优</t>
         </is>
       </c>
-      <c r="D21" s="95" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>网格最佳</t>
         </is>
       </c>
-      <c r="E21" s="95" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>买入持有</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="96" t="inlineStr">
+    <row r="22" ht="14.5" customHeight="1" s="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>2021年</t>
         </is>
       </c>
-      <c r="B22" s="96" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>+1.0%</t>
         </is>
       </c>
-      <c r="C22" s="97" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>+4.3%</t>
         </is>
       </c>
-      <c r="D22" s="96" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>+1.2%</t>
         </is>
       </c>
-      <c r="E22" s="96" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>-1.3%</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="96" t="inlineStr">
+    <row r="23" ht="14.5" customHeight="1" s="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2022年</t>
         </is>
       </c>
-      <c r="B23" s="96" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>-6.4%</t>
         </is>
       </c>
-      <c r="C23" s="97" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>-2.4%</t>
         </is>
       </c>
-      <c r="D23" s="96" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>-4.4%</t>
         </is>
       </c>
-      <c r="E23" s="96" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>-6.2%</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="96" t="inlineStr">
+    <row r="24" ht="14.5" customHeight="1" s="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>2023年</t>
         </is>
       </c>
-      <c r="B24" s="96" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>+0.8%</t>
         </is>
       </c>
-      <c r="C24" s="97" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>-1.1%</t>
         </is>
       </c>
-      <c r="D24" s="96" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>+0.1%</t>
         </is>
       </c>
-      <c r="E24" s="96" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>+2.0%</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="96" t="inlineStr">
+    <row r="25" ht="14.5" customHeight="1" s="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2024年</t>
         </is>
       </c>
-      <c r="B25" s="96" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>+11.4%</t>
         </is>
       </c>
-      <c r="C25" s="97" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>+13.4%</t>
         </is>
       </c>
-      <c r="D25" s="96" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>+27.0%</t>
         </is>
       </c>
-      <c r="E25" s="96" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>+13.9%</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="96" t="inlineStr">
+    <row r="26" ht="14.5" customHeight="1" s="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="B26" s="96" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>+21.6%</t>
         </is>
       </c>
-      <c r="C26" s="97" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>+22.0%</t>
         </is>
       </c>
-      <c r="D26" s="96" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>+19.3%</t>
         </is>
       </c>
-      <c r="E26" s="96" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>+23.4%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="96" t="inlineStr">
+    <row r="27" ht="14.5" customHeight="1" s="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="B27" s="96" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>+5.2%</t>
         </is>
       </c>
-      <c r="C27" s="97" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>+6.7%</t>
         </is>
       </c>
-      <c r="D27" s="96" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>+4.5%</t>
         </is>
       </c>
-      <c r="E27" s="96" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>+5.8%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="98" t="inlineStr">
+    <row r="29" ht="16.5" customHeight="1" s="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>四、GA最优方案详细参数</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="99" t="inlineStr">
+    <row r="30" ht="14.5" customHeight="1" s="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>止盈触发 (sp_trigger)</t>
         </is>
       </c>
-      <c r="B30" s="96" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>&gt;= +5.1%</t>
         </is>
       </c>
-      <c r="C30" s="103" t="n"/>
-      <c r="D30" s="103" t="n"/>
-      <c r="E30" s="104" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="99" t="inlineStr">
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="29" customHeight="1" s="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>止盈卖出比例 (sp_sell_ratio)</t>
         </is>
       </c>
-      <c r="B31" s="96" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>100%（全部卖出）</t>
         </is>
       </c>
-      <c r="C31" s="103" t="n"/>
-      <c r="D31" s="103" t="n"/>
-      <c r="E31" s="104" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="99" t="inlineStr">
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="14.5" customHeight="1" s="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>止损触发 (sl_trigger)</t>
         </is>
       </c>
-      <c r="B32" s="96" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>&lt;= -19.9%（实操约-20%）</t>
         </is>
       </c>
-      <c r="C32" s="103" t="n"/>
-      <c r="D32" s="103" t="n"/>
-      <c r="E32" s="104" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="99" t="inlineStr">
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="14.5" customHeight="1" s="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>观察期 (observe_days)</t>
         </is>
       </c>
-      <c r="B33" s="96" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>32个交易日（约45自然日）</t>
         </is>
       </c>
-      <c r="C33" s="103" t="n"/>
-      <c r="D33" s="103" t="n"/>
-      <c r="E33" s="104" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="99" t="inlineStr">
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="14.5" customHeight="1" s="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>再平衡频率 (rb_freq)</t>
         </is>
       </c>
-      <c r="B34" s="96" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>年度（12月末）</t>
         </is>
       </c>
-      <c r="C34" s="103" t="n"/>
-      <c r="D34" s="103" t="n"/>
-      <c r="E34" s="104" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="99" t="inlineStr">
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="29" customHeight="1" s="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>再平衡阈值 (rb_threshold)</t>
         </is>
       </c>
-      <c r="B35" s="96" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>偏离&gt;=±28%触发</t>
         </is>
       </c>
-      <c r="C35" s="103" t="n"/>
-      <c r="D35" s="103" t="n"/>
-      <c r="E35" s="104" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="99" t="inlineStr">
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="14.5" customHeight="1" s="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>回测CAGR</t>
         </is>
       </c>
-      <c r="B36" s="96" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>+7.00%</t>
         </is>
       </c>
-      <c r="C36" s="103" t="n"/>
-      <c r="D36" s="103" t="n"/>
-      <c r="E36" s="104" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="99" t="inlineStr">
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="14.5" customHeight="1" s="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>累计收益</t>
         </is>
       </c>
-      <c r="B37" s="96" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>+38.47%（400万→553.9万）</t>
         </is>
       </c>
-      <c r="C37" s="103" t="n"/>
-      <c r="D37" s="103" t="n"/>
-      <c r="E37" s="104" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="99" t="inlineStr">
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="14.5" customHeight="1" s="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>最大回撤</t>
         </is>
       </c>
-      <c r="B38" s="96" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>-8.89%</t>
         </is>
       </c>
-      <c r="C38" s="103" t="n"/>
-      <c r="D38" s="103" t="n"/>
-      <c r="E38" s="104" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="99" t="inlineStr">
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="14.5" customHeight="1" s="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>夏普比率</t>
         </is>
       </c>
-      <c r="B39" s="96" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>1.037</t>
         </is>
       </c>
-      <c r="C39" s="103" t="n"/>
-      <c r="D39" s="103" t="n"/>
-      <c r="E39" s="104" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="99" t="inlineStr">
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="14.5" customHeight="1" s="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>总交易笔数</t>
         </is>
       </c>
-      <c r="B40" s="96" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>66笔</t>
         </is>
       </c>
-      <c r="C40" s="103" t="n"/>
-      <c r="D40" s="103" t="n"/>
-      <c r="E40" s="104" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="99" t="inlineStr">
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="14.5" customHeight="1" s="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="B41" s="96" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>当前按V3执行，正式迁移时参考此方案</t>
         </is>
       </c>
-      <c r="C41" s="103" t="n"/>
-      <c r="D41" s="103" t="n"/>
-      <c r="E41" s="104" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="101" t="inlineStr">
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="102" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>1. 回测区间：2021-01-01 ~ 2025-12-31，初始400万元</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="102" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>2. 由遗传算法(60个体x50代=3000次回测)搜索得到</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="102" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>3. 当前仍按V3方案执行，GA方案仅存档备查</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="102" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>4. 后续如需切换，需同步修改update_portfolio.py中的信号检测规则</t>
         </is>
@@ -18680,8 +19213,8 @@
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B41:E41"/>

--- a/400万资产配置组合2026.xlsx
+++ b/400万资产配置组合2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投资纪要" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,19 +21,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="[$-409]yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="170" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="0.0000%"/>
-    <numFmt numFmtId="172" formatCode="0.000%"/>
-    <numFmt numFmtId="173" formatCode="0.0000"/>
-    <numFmt numFmtId="174" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
-    <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="0.0000%"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="173" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
+    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -856,14 +855,16 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -872,7 +873,7 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -881,7 +882,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -890,7 +891,7 @@
     <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -908,10 +909,10 @@
     <xf numFmtId="9" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -920,13 +921,13 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -943,22 +944,22 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -991,7 +992,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1000,10 +1001,10 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1012,7 +1013,7 @@
     <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1021,10 +1022,10 @@
     <xf numFmtId="167" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1033,13 +1034,13 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1049,10 +1050,10 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1061,16 +1062,16 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1083,8 +1084,10 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2470,10 +2473,10 @@
         <v>0.1875</v>
       </c>
       <c r="F2" s="82" t="n">
-        <v>0.2234</v>
+        <v>0.2273</v>
       </c>
       <c r="G2" s="82" t="n">
-        <v>0.0359</v>
+        <v>0.0398</v>
       </c>
       <c r="H2" s="83" t="n">
         <v>4.885</v>
@@ -2522,10 +2525,10 @@
         <v>0.0625</v>
       </c>
       <c r="F3" s="92" t="n">
-        <v>0.0184</v>
+        <v>0.0187</v>
       </c>
       <c r="G3" s="92" t="n">
-        <v>-0.0441</v>
+        <v>-0.0438</v>
       </c>
       <c r="H3" s="93" t="n">
         <v>1.838</v>
@@ -2576,10 +2579,10 @@
         <v>0.0625</v>
       </c>
       <c r="F4" s="82" t="n">
-        <v>0.0761</v>
+        <v>0.0775</v>
       </c>
       <c r="G4" s="82" t="n">
-        <v>0.0136</v>
+        <v>0.015</v>
       </c>
       <c r="H4" s="86" t="n">
         <v>3.968</v>
@@ -2627,10 +2630,10 @@
         <v>0.0625</v>
       </c>
       <c r="F5" s="82" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="G5" s="82" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="H5" s="86" t="n">
         <v>1.15</v>
@@ -2674,10 +2677,10 @@
         <v>0.125</v>
       </c>
       <c r="F6" s="92" t="n">
-        <v>0.0605</v>
+        <v>0.0616</v>
       </c>
       <c r="G6" s="92" t="n">
-        <v>-0.0645</v>
+        <v>-0.0634</v>
       </c>
       <c r="H6" s="93" t="n">
         <v>13.8644</v>
@@ -2724,10 +2727,10 @@
         <v>0.125</v>
       </c>
       <c r="F7" s="82" t="n">
-        <v>0.1493</v>
+        <v>0.1519</v>
       </c>
       <c r="G7" s="82" t="n">
-        <v>0.0243</v>
+        <v>0.0269</v>
       </c>
       <c r="H7" s="86" t="n">
         <v>135.645</v>
@@ -2771,10 +2774,10 @@
         <v>0.125</v>
       </c>
       <c r="F8" s="82" t="n">
-        <v>0.1475</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="82" t="n">
-        <v>0.0225</v>
+        <v>0.025</v>
       </c>
       <c r="H8" s="86" t="n">
         <v>141.2121</v>
@@ -2818,29 +2821,28 @@
         <v>0.0625</v>
       </c>
       <c r="F9" s="82" t="n">
-        <v>0.0919</v>
+        <v>0.0762</v>
       </c>
       <c r="G9" s="82" t="n">
-        <v>0.0294</v>
+        <v>0.0137</v>
       </c>
       <c r="H9" s="86" t="n">
-        <v>113.4903</v>
+        <v>113.462</v>
       </c>
       <c r="I9" s="84" t="n">
-        <v>2700</v>
-      </c>
-      <c r="J9" s="85">
-        <f>H9*I9</f>
-        <v/>
+        <v>2200</v>
+      </c>
+      <c r="J9" s="85" t="n">
+        <v>249616.4</v>
       </c>
       <c r="K9" s="96" t="n">
         <v>113.626</v>
       </c>
       <c r="L9" s="87" t="n">
-        <v>366.39</v>
+        <v>360.8</v>
       </c>
       <c r="M9" s="88" t="n">
-        <v>0.0012</v>
+        <v>0.0014</v>
       </c>
       <c r="N9" s="35" t="n"/>
       <c r="O9" s="89" t="n"/>
@@ -2865,10 +2867,10 @@
         <v>0.1875</v>
       </c>
       <c r="F10" s="92" t="n">
-        <v>0.1619</v>
+        <v>0.1647</v>
       </c>
       <c r="G10" s="92" t="n">
-        <v>-0.0256</v>
+        <v>-0.0228</v>
       </c>
       <c r="H10" s="98" t="n">
         <v>9.1196</v>
@@ -2949,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20.8181818181818" customWidth="1" style="100" min="1" max="1"/>
@@ -3631,55 +3633,26 @@
       <c r="A27" s="104" t="n">
         <v>46205</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="16" t="n">
         <v>588050</v>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="102" t="n">
         <v>2.121</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="94" t="n">
         <v>-30000</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="95" t="n">
         <v>-63630</v>
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
           <t>卖出止盈</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="105" t="n">
-        <v>46205</v>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>511360</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>短融ETF</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>113.615</v>
-      </c>
-      <c r="E28" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="F28" s="0" t="n">
-        <v>56807.5</v>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>止盈转入</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16412,7 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B232" s="0" t="inlineStr">
@@ -16494,7 +16467,7 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B233" s="0" t="inlineStr">
@@ -16549,7 +16522,7 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B234" s="0" t="inlineStr">
@@ -16604,7 +16577,7 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B235" s="0" t="inlineStr">
@@ -16659,7 +16632,7 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B236" s="0" t="inlineStr">
@@ -16711,7 +16684,7 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B237" s="0" t="inlineStr">
@@ -16766,7 +16739,7 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B238" s="0" t="inlineStr">
@@ -16821,7 +16794,7 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B239" s="0" t="inlineStr">
@@ -16873,7 +16846,7 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B240" s="0" t="inlineStr">
@@ -16926,9 +16899,9 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A241" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B241" s="0" t="inlineStr">
@@ -16941,49 +16914,23 @@
           <t>510300</t>
         </is>
       </c>
-      <c r="D241" s="0" t="n">
-        <v>153800</v>
-      </c>
-      <c r="E241" s="0" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="F241" s="0" t="n">
-        <v>751313</v>
-      </c>
       <c r="G241" s="0" t="n">
-        <v>4.959</v>
+        <v>5.019</v>
       </c>
       <c r="H241" s="0" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="I241" s="0" t="n">
-        <v>762694.2</v>
+        <v>0.0274</v>
       </c>
       <c r="J241" s="0" t="n">
-        <v>11381.2</v>
+        <v>20609.2</v>
       </c>
       <c r="K241" s="0" t="n">
-        <v>0.0151</v>
-      </c>
-      <c r="L241" s="0" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="M241" s="0" t="n">
-        <v>0.2257</v>
-      </c>
-      <c r="N241" s="0" t="n">
-        <v>0.0382</v>
-      </c>
-      <c r="O241" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2.74</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A242" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B242" s="0" t="inlineStr">
@@ -16996,49 +16943,23 @@
           <t>588050</t>
         </is>
       </c>
-      <c r="D242" s="0" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E242" s="0" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="F242" s="0" t="n">
-        <v>110280</v>
-      </c>
       <c r="G242" s="0" t="n">
-        <v>2.182</v>
+        <v>2.277</v>
       </c>
       <c r="H242" s="0" t="n">
-        <v>0.0506</v>
-      </c>
-      <c r="I242" s="0" t="n">
-        <v>130920</v>
+        <v>0.2388</v>
       </c>
       <c r="J242" s="0" t="n">
-        <v>20640</v>
+        <v>26340</v>
       </c>
       <c r="K242" s="0" t="n">
-        <v>0.1872</v>
-      </c>
-      <c r="L242" s="0" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="M242" s="0" t="n">
-        <v>0.0387</v>
-      </c>
-      <c r="N242" s="0" t="n">
-        <v>-0.0238</v>
-      </c>
-      <c r="O242" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>23.88</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A243" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B243" s="0" t="inlineStr">
@@ -17051,49 +16972,23 @@
           <t>159915</t>
         </is>
       </c>
-      <c r="D243" s="0" t="n">
-        <v>63000</v>
-      </c>
-      <c r="E243" s="0" t="n">
-        <v>3.968</v>
-      </c>
-      <c r="F243" s="0" t="n">
-        <v>249984</v>
-      </c>
       <c r="G243" s="0" t="n">
-        <v>4.236</v>
+        <v>4.364</v>
       </c>
       <c r="H243" s="0" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I243" s="0" t="n">
-        <v>266868</v>
+        <v>0.0998</v>
       </c>
       <c r="J243" s="0" t="n">
-        <v>16884</v>
+        <v>24948</v>
       </c>
       <c r="K243" s="0" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="L243" s="0" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="M243" s="0" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N243" s="0" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="O243" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>9.98</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A244" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B244" s="0" t="inlineStr">
@@ -17106,49 +17001,23 @@
           <t>512890</t>
         </is>
       </c>
-      <c r="D244" s="0" t="n">
-        <v>218000</v>
-      </c>
-      <c r="E244" s="0" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F244" s="0" t="n">
-        <v>250700</v>
-      </c>
       <c r="G244" s="0" t="n">
-        <v>1.089</v>
+        <v>1.067</v>
       </c>
       <c r="H244" s="0" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="I244" s="0" t="n">
-        <v>237402</v>
+        <v>-0.0722</v>
       </c>
       <c r="J244" s="0" t="n">
-        <v>-13298</v>
+        <v>-18094</v>
       </c>
       <c r="K244" s="0" t="n">
-        <v>-0.053</v>
-      </c>
-      <c r="L244" s="0" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="M244" s="0" t="n">
-        <v>0.0703</v>
-      </c>
-      <c r="N244" s="0" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="O244" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A245" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B245" s="0" t="inlineStr">
@@ -17161,46 +17030,23 @@
           <t>511380</t>
         </is>
       </c>
-      <c r="D245" s="0" t="n">
-        <v>14500</v>
-      </c>
-      <c r="E245" s="0" t="n">
-        <v>13.8644</v>
-      </c>
-      <c r="F245" s="0" t="n">
-        <v>201033.8</v>
-      </c>
       <c r="G245" s="0" t="n">
-        <v>13.792</v>
-      </c>
-      <c r="I245" s="0" t="n">
-        <v>199984</v>
+        <v>13.954</v>
+      </c>
+      <c r="H245" s="0" t="n">
+        <v>0.0065</v>
       </c>
       <c r="J245" s="0" t="n">
-        <v>-1049.8</v>
+        <v>1299.2</v>
       </c>
       <c r="K245" s="0" t="n">
-        <v>-0.0052</v>
-      </c>
-      <c r="L245" s="0" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M245" s="0" t="n">
-        <v>0.0592</v>
-      </c>
-      <c r="N245" s="0" t="n">
-        <v>-0.0658</v>
-      </c>
-      <c r="O245" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.65</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A246" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B246" s="0" t="inlineStr">
@@ -17213,156 +17059,81 @@
           <t>511260</t>
         </is>
       </c>
-      <c r="D246" s="0" t="n">
-        <v>3700</v>
-      </c>
-      <c r="E246" s="0" t="n">
-        <v>135.645</v>
-      </c>
-      <c r="F246" s="0" t="n">
-        <v>501886.5</v>
-      </c>
       <c r="G246" s="0" t="n">
-        <v>134.97</v>
+        <v>134.854</v>
       </c>
       <c r="H246" s="0" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="J246" s="0" t="n">
+        <v>-2926.7</v>
+      </c>
+      <c r="K246" s="0" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>5年国债ETF</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>511010</t>
+        </is>
+      </c>
+      <c r="G247" s="0" t="n">
+        <v>140.792</v>
+      </c>
+      <c r="H247" s="0" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="J247" s="0" t="n">
+        <v>-1470.35</v>
+      </c>
+      <c r="K247" s="0" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>短融ETF</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>511360</t>
+        </is>
+      </c>
+      <c r="G248" s="0" t="n">
+        <v>113.61</v>
+      </c>
+      <c r="H248" s="0" t="n">
         <v>0.0013</v>
       </c>
-      <c r="I246" s="0" t="n">
-        <v>499389</v>
-      </c>
-      <c r="J246" s="0" t="n">
-        <v>-2497.5</v>
-      </c>
-      <c r="K246" s="0" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="L246" s="0" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M246" s="0" t="n">
-        <v>0.1478</v>
-      </c>
-      <c r="N246" s="0" t="n">
-        <v>0.0228</v>
-      </c>
-      <c r="O246" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="B247" s="0" t="inlineStr">
-        <is>
-          <t>5年国债ETF</t>
-        </is>
-      </c>
-      <c r="C247" s="0" t="inlineStr">
-        <is>
-          <t>511010</t>
-        </is>
-      </c>
-      <c r="D247" s="0" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E247" s="0" t="n">
-        <v>141.2121</v>
-      </c>
-      <c r="F247" s="0" t="n">
-        <v>494242.35</v>
-      </c>
-      <c r="G247" s="0" t="n">
-        <v>140.845</v>
-      </c>
-      <c r="H247" s="0" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="I247" s="0" t="n">
-        <v>492957.5</v>
-      </c>
-      <c r="J247" s="0" t="n">
-        <v>-1284.85</v>
-      </c>
-      <c r="K247" s="0" t="n">
-        <v>-0.0026</v>
-      </c>
-      <c r="L247" s="0" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M247" s="0" t="n">
-        <v>0.1459</v>
-      </c>
-      <c r="N247" s="0" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="O247" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
-      </c>
-      <c r="B248" s="0" t="inlineStr">
-        <is>
-          <t>短融ETF</t>
-        </is>
-      </c>
-      <c r="C248" s="0" t="inlineStr">
-        <is>
-          <t>511360</t>
-        </is>
-      </c>
-      <c r="D248" s="0" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E248" s="0" t="n">
-        <v>113.462</v>
-      </c>
-      <c r="F248" s="0" t="n">
-        <v>249616.4</v>
-      </c>
-      <c r="G248" s="0" t="n">
-        <v>113.597</v>
-      </c>
-      <c r="I248" s="0" t="n">
-        <v>249913.4</v>
-      </c>
       <c r="J248" s="0" t="n">
-        <v>297</v>
+        <v>325.6</v>
       </c>
       <c r="K248" s="0" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="L248" s="0" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="M248" s="0" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="N248" s="0" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="O248" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.13</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="0" t="inlineStr">
-        <is>
-          <t>20260629</t>
+      <c r="A249" s="105" t="inlineStr">
+        <is>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B249" s="0" t="inlineStr">
@@ -17375,43 +17146,17 @@
           <t>518880</t>
         </is>
       </c>
-      <c r="D249" s="0" t="n">
-        <v>63800</v>
-      </c>
-      <c r="E249" s="0" t="n">
-        <v>9.1196</v>
-      </c>
-      <c r="F249" s="0" t="n">
-        <v>581830.48</v>
-      </c>
       <c r="G249" s="0" t="n">
-        <v>8.449</v>
+        <v>8.378</v>
       </c>
       <c r="H249" s="0" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I249" s="0" t="n">
-        <v>539046.2</v>
+        <v>-0.0813</v>
       </c>
       <c r="J249" s="0" t="n">
-        <v>-42784.28</v>
+        <v>-47314.08</v>
       </c>
       <c r="K249" s="0" t="n">
-        <v>-0.0735</v>
-      </c>
-      <c r="L249" s="0" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="M249" s="0" t="n">
-        <v>0.1595</v>
-      </c>
-      <c r="N249" s="0" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="O249" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -17907,495 +17652,495 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="0" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B259" s="0" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>沪深300ETF</t>
         </is>
       </c>
-      <c r="C259" s="0" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>510300</t>
         </is>
       </c>
-      <c r="D259" s="0" t="n">
+      <c r="D259" t="n">
         <v>153800</v>
       </c>
-      <c r="E259" s="0" t="n">
+      <c r="E259" t="n">
         <v>4.885</v>
       </c>
-      <c r="F259" s="0" t="n">
+      <c r="F259" t="n">
         <v>751313</v>
       </c>
-      <c r="G259" s="0" t="n">
+      <c r="G259" t="n">
         <v>4.85</v>
       </c>
-      <c r="H259" s="0" t="n">
+      <c r="H259" t="n">
         <v>-0.0296</v>
       </c>
-      <c r="I259" s="0" t="n">
+      <c r="I259" t="n">
         <v>745930</v>
       </c>
-      <c r="J259" s="0" t="n">
+      <c r="J259" t="n">
         <v>-5383</v>
       </c>
-      <c r="K259" s="0" t="n">
+      <c r="K259" t="n">
         <v>-0.0072</v>
       </c>
-      <c r="L259" s="0" t="n">
+      <c r="L259" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M259" s="0" t="n">
-        <v>0.2234</v>
-      </c>
-      <c r="N259" s="0" t="n">
-        <v>0.0359</v>
-      </c>
-      <c r="O259" s="0" t="inlineStr">
+      <c r="M259" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="O259" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="0" t="inlineStr">
+      <c r="A260" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B260" s="0" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>科创50ETF</t>
         </is>
       </c>
-      <c r="C260" s="0" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>588050</t>
         </is>
       </c>
-      <c r="D260" s="0" t="n">
+      <c r="D260" t="n">
         <v>30000</v>
       </c>
-      <c r="E260" s="0" t="n">
+      <c r="E260" t="n">
         <v>1.838</v>
       </c>
-      <c r="F260" s="0" t="n">
+      <c r="F260" t="n">
         <v>55140</v>
       </c>
-      <c r="G260" s="0" t="n">
+      <c r="G260" t="n">
         <v>2.044</v>
       </c>
-      <c r="H260" s="0" t="n">
+      <c r="H260" t="n">
         <v>-0.0789</v>
       </c>
-      <c r="I260" s="0" t="n">
+      <c r="I260" t="n">
         <v>61320</v>
       </c>
-      <c r="J260" s="0" t="n">
+      <c r="J260" t="n">
         <v>6180</v>
       </c>
-      <c r="K260" s="0" t="n">
+      <c r="K260" t="n">
         <v>0.1121</v>
       </c>
-      <c r="L260" s="0" t="n">
+      <c r="L260" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M260" s="0" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="N260" s="0" t="n">
-        <v>-0.0441</v>
-      </c>
-      <c r="O260" s="0" t="inlineStr">
+      <c r="M260" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="N260" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="O260" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="0" t="inlineStr">
+      <c r="A261" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B261" s="0" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>创业板ETF</t>
         </is>
       </c>
-      <c r="C261" s="0" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>159915</t>
         </is>
       </c>
-      <c r="D261" s="0" t="n">
+      <c r="D261" t="n">
         <v>63000</v>
       </c>
-      <c r="E261" s="0" t="n">
+      <c r="E261" t="n">
         <v>3.968</v>
       </c>
-      <c r="F261" s="0" t="n">
+      <c r="F261" t="n">
         <v>249984</v>
       </c>
-      <c r="G261" s="0" t="n">
+      <c r="G261" t="n">
         <v>4.036</v>
       </c>
-      <c r="H261" s="0" t="n">
+      <c r="H261" t="n">
         <v>-0.0557</v>
       </c>
-      <c r="I261" s="0" t="n">
+      <c r="I261" t="n">
         <v>254268</v>
       </c>
-      <c r="J261" s="0" t="n">
+      <c r="J261" t="n">
         <v>4284</v>
       </c>
-      <c r="K261" s="0" t="n">
+      <c r="K261" t="n">
         <v>0.0171</v>
       </c>
-      <c r="L261" s="0" t="n">
+      <c r="L261" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M261" s="0" t="n">
-        <v>0.0761</v>
-      </c>
-      <c r="N261" s="0" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="O261" s="0" t="inlineStr">
+      <c r="M261" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O261" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="0" t="inlineStr">
+      <c r="A262" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B262" s="0" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>红利低波ETF</t>
         </is>
       </c>
-      <c r="C262" s="0" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
       </c>
-      <c r="D262" s="0" t="n">
+      <c r="D262" t="n">
         <v>218000</v>
       </c>
-      <c r="E262" s="0" t="n">
+      <c r="E262" t="n">
         <v>1.15</v>
       </c>
-      <c r="F262" s="0" t="n">
+      <c r="F262" t="n">
         <v>250700</v>
       </c>
-      <c r="G262" s="0" t="n">
+      <c r="G262" t="n">
         <v>1.087</v>
       </c>
-      <c r="H262" s="0" t="n">
+      <c r="H262" t="n">
         <v>0.0074</v>
       </c>
-      <c r="I262" s="0" t="n">
+      <c r="I262" t="n">
         <v>236966</v>
       </c>
-      <c r="J262" s="0" t="n">
+      <c r="J262" t="n">
         <v>-13734</v>
       </c>
-      <c r="K262" s="0" t="n">
+      <c r="K262" t="n">
         <v>-0.0548</v>
       </c>
-      <c r="L262" s="0" t="n">
+      <c r="L262" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M262" s="0" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="N262" s="0" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="O262" s="0" t="inlineStr">
+      <c r="M262" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="O262" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="0" t="inlineStr">
+      <c r="A263" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B263" s="0" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>可转债ETF</t>
         </is>
       </c>
-      <c r="C263" s="0" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>511380</t>
         </is>
       </c>
-      <c r="D263" s="0" t="n">
+      <c r="D263" t="n">
         <v>14500</v>
       </c>
-      <c r="E263" s="0" t="n">
+      <c r="E263" t="n">
         <v>13.8644</v>
       </c>
-      <c r="F263" s="0" t="n">
+      <c r="F263" t="n">
         <v>201033.8</v>
       </c>
-      <c r="G263" s="0" t="n">
+      <c r="G263" t="n">
         <v>13.942</v>
       </c>
-      <c r="H263" s="0" t="n">
+      <c r="H263" t="n">
         <v>-0.0044</v>
       </c>
-      <c r="I263" s="0" t="n">
+      <c r="I263" t="n">
         <v>202159</v>
       </c>
-      <c r="J263" s="0" t="n">
+      <c r="J263" t="n">
         <v>1125.2</v>
       </c>
-      <c r="K263" s="0" t="n">
+      <c r="K263" t="n">
         <v>0.0056</v>
       </c>
-      <c r="L263" s="0" t="n">
+      <c r="L263" t="n">
         <v>0.125</v>
       </c>
-      <c r="M263" s="0" t="n">
-        <v>0.0605</v>
-      </c>
-      <c r="N263" s="0" t="n">
-        <v>-0.0645</v>
-      </c>
-      <c r="O263" s="0" t="inlineStr">
+      <c r="M263" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="N263" t="n">
+        <v>-0.0634</v>
+      </c>
+      <c r="O263" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="0" t="inlineStr">
+      <c r="A264" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B264" s="0" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>10年国债ETF</t>
         </is>
       </c>
-      <c r="C264" s="0" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>511260</t>
         </is>
       </c>
-      <c r="D264" s="0" t="n">
+      <c r="D264" t="n">
         <v>3700</v>
       </c>
-      <c r="E264" s="0" t="n">
+      <c r="E264" t="n">
         <v>135.645</v>
       </c>
-      <c r="F264" s="0" t="n">
+      <c r="F264" t="n">
         <v>501886.5</v>
       </c>
-      <c r="G264" s="0" t="n">
+      <c r="G264" t="n">
         <v>134.766</v>
       </c>
-      <c r="H264" s="0" t="n">
+      <c r="H264" t="n">
         <v>0.0008</v>
       </c>
-      <c r="I264" s="0" t="n">
+      <c r="I264" t="n">
         <v>498634.2</v>
       </c>
-      <c r="J264" s="0" t="n">
+      <c r="J264" t="n">
         <v>-3252.3</v>
       </c>
-      <c r="K264" s="0" t="n">
+      <c r="K264" t="n">
         <v>-0.0065</v>
       </c>
-      <c r="L264" s="0" t="n">
+      <c r="L264" t="n">
         <v>0.125</v>
       </c>
-      <c r="M264" s="0" t="n">
-        <v>0.1493</v>
-      </c>
-      <c r="N264" s="0" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="O264" s="0" t="inlineStr">
+      <c r="M264" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="O264" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="0" t="inlineStr">
+      <c r="A265" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B265" s="0" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>5年国债ETF</t>
         </is>
       </c>
-      <c r="C265" s="0" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>511010</t>
         </is>
       </c>
-      <c r="D265" s="0" t="n">
+      <c r="D265" t="n">
         <v>3500</v>
       </c>
-      <c r="E265" s="0" t="n">
+      <c r="E265" t="n">
         <v>141.2121</v>
       </c>
-      <c r="F265" s="0" t="n">
+      <c r="F265" t="n">
         <v>494242.35</v>
       </c>
-      <c r="G265" s="0" t="n">
+      <c r="G265" t="n">
         <v>140.695</v>
       </c>
-      <c r="H265" s="0" t="n">
+      <c r="H265" t="n">
         <v>0.0004</v>
       </c>
-      <c r="I265" s="0" t="n">
+      <c r="I265" t="n">
         <v>492432.5</v>
       </c>
-      <c r="J265" s="0" t="n">
+      <c r="J265" t="n">
         <v>-1809.85</v>
       </c>
-      <c r="K265" s="0" t="n">
+      <c r="K265" t="n">
         <v>-0.0037</v>
       </c>
-      <c r="L265" s="0" t="n">
+      <c r="L265" t="n">
         <v>0.125</v>
       </c>
-      <c r="M265" s="0" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="N265" s="0" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="O265" s="0" t="inlineStr">
+      <c r="M265" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="O265" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="0" t="inlineStr">
+      <c r="A266" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B266" s="0" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>短融ETF</t>
         </is>
       </c>
-      <c r="C266" s="0" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>511360</t>
         </is>
       </c>
-      <c r="D266" s="0" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E266" s="0" t="n">
-        <v>113.4903</v>
-      </c>
-      <c r="F266" s="0" t="n">
-        <v>306423.81</v>
-      </c>
-      <c r="G266" s="0" t="n">
+      <c r="D266" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E266" t="n">
+        <v>113.462</v>
+      </c>
+      <c r="F266" t="n">
+        <v>249616.4</v>
+      </c>
+      <c r="G266" t="n">
         <v>113.626</v>
       </c>
-      <c r="H266" s="0" t="n">
+      <c r="H266" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I266" s="0" t="n">
-        <v>306790.2</v>
-      </c>
-      <c r="J266" s="0" t="n">
-        <v>366.39</v>
-      </c>
-      <c r="K266" s="0" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="L266" s="0" t="n">
+      <c r="I266" t="n">
+        <v>249977.2</v>
+      </c>
+      <c r="J266" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="L266" t="n">
         <v>0.0625</v>
       </c>
-      <c r="M266" s="0" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="N266" s="0" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="O266" s="0" t="inlineStr">
+      <c r="M266" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="O266" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="0" t="inlineStr">
+      <c r="A267" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
       </c>
-      <c r="B267" s="0" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>黄金ETF</t>
         </is>
       </c>
-      <c r="C267" s="0" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>518880</t>
         </is>
       </c>
-      <c r="D267" s="0" t="n">
+      <c r="D267" t="n">
         <v>63800</v>
       </c>
-      <c r="E267" s="0" t="n">
+      <c r="E267" t="n">
         <v>9.1196</v>
       </c>
-      <c r="F267" s="0" t="n">
+      <c r="F267" t="n">
         <v>581830.48</v>
       </c>
-      <c r="G267" s="0" t="n">
+      <c r="G267" t="n">
         <v>8.475</v>
       </c>
-      <c r="H267" s="0" t="n">
+      <c r="H267" t="n">
         <v>0.0247</v>
       </c>
-      <c r="I267" s="0" t="n">
+      <c r="I267" t="n">
         <v>540705</v>
       </c>
-      <c r="J267" s="0" t="n">
+      <c r="J267" t="n">
         <v>-41125.48</v>
       </c>
-      <c r="K267" s="0" t="n">
+      <c r="K267" t="n">
         <v>-0.0707</v>
       </c>
-      <c r="L267" s="0" t="n">
+      <c r="L267" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M267" s="0" t="n">
-        <v>0.1619</v>
-      </c>
-      <c r="N267" s="0" t="n">
-        <v>-0.0256</v>
-      </c>
-      <c r="O267" s="0" t="inlineStr">
+      <c r="M267" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="N267" t="n">
+        <v>-0.0228</v>
+      </c>
+      <c r="O267" t="inlineStr">
         <is>
           <t>—</t>
         </is>
